--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -57,7 +57,18 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
       <color rgb="00404040"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="001F4E79"/>
       <sz val="9"/>
     </font>
     <font>
@@ -69,6 +80,12 @@
     <font>
       <name val="맑은 고딕"/>
       <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
       <sz val="9"/>
     </font>
     <font>
@@ -90,17 +107,12 @@
     </font>
     <font>
       <name val="맑은 고딕"/>
-      <color rgb="001F4E79"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="맑은 고딕"/>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -114,12 +126,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F7F9FC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF9E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -226,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -242,66 +264,78 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -669,15 +703,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -719,15 +755,25 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t>현황</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
           <t>담당 컴포넌트</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>수정 대상</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>오류코드</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>오류코드명</t>
         </is>
@@ -743,81 +789,113 @@
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="7" t="inlineStr"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Request ID 생성 또는 검증</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr"/>
-      <c r="D7" s="13" t="inlineStr"/>
-      <c r="E7" s="14" t="inlineStr"/>
-      <c r="F7" s="15" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr"/>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="inlineStr"/>
+      <c r="F7" s="16" t="inlineStr"/>
+      <c r="G7" s="17" t="inlineStr"/>
+      <c r="H7" s="18" t="inlineStr"/>
     </row>
     <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>호출 Client 검증</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>(1) 필수 Header 의 X-Client-ID 가 아예 입력되지 않았는지 필수입력값 유효성을 체크한다.
 → 입력되어 있으면 (2) 단계 진행</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>RequestContextResolver
 resolve(HttpServletRequest,
           serviceId, request)</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>HttpHeaderRequestContextResolver.java</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>BS-VAL-001
 HTTP 400</t>
         </is>
       </c>
-      <c r="F8" s="21" t="inlineStr">
+      <c r="H8" s="25" t="inlineStr">
         <is>
           <t>Client ID 미입력</t>
         </is>
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="22" t="n"/>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="A9" s="26" t="n"/>
+      <c r="B9" s="26" t="n"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>(2) BS_CLIENT 테이블의 PK 인 client_id 값이 X-Client-ID 와 같은 데이터가 있는지 체크하고,
 있으면 해당 데이터의 active_yn 컬럼값이 'Y' 인지 체크한다.
 → 'Y' 이면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>ClientAuthenticationService
 authenticate(ServiceContext)</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>DummyClientAuthenticationService.java</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-001
 HTTP 401</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="H9" s="25" t="inlineStr">
         <is>
           <t>미등록 Client
 미사용 Client</t>
@@ -825,163 +903,219 @@
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="10" t="n">
+      <c r="A10" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>SSO 사용자 Context 추출</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="13" t="inlineStr"/>
-      <c r="E10" s="14" t="inlineStr"/>
-      <c r="F10" s="15" t="inlineStr"/>
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>미대상</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr"/>
+      <c r="F10" s="16" t="inlineStr"/>
+      <c r="G10" s="17" t="inlineStr"/>
+      <c r="H10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="16" t="n">
+      <c r="A11" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Service Catalog에서 활성 버전 조회</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>(1) service ID 가 존재하는지
 → 존재하면 (2)</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>InMemoryServiceMetadataRepository.java</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="H11" s="25" t="inlineStr">
         <is>
           <t>서비스 미존재</t>
         </is>
       </c>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="23" t="n"/>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="A12" s="28" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>(2) 해당 service ID의 사용여부가 "사용" 상태인지
 → 사용상태면 (3)</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>InMemoryServiceMetadataRepository.java</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="F12" s="21" t="inlineStr">
+      <c r="H12" s="25" t="inlineStr">
         <is>
           <t>서비스 미사용</t>
         </is>
       </c>
     </row>
     <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="23" t="n"/>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="A13" s="28" t="n"/>
+      <c r="B13" s="28" t="n"/>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>(3) 버전 정보가 존재하는지
 → 존재하면 (4)</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="E13" s="20" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>InMemoryServiceMetadataRepository.java</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="H13" s="25" t="inlineStr">
         <is>
           <t>버전 미존재</t>
         </is>
       </c>
     </row>
     <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="22" t="n"/>
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="A14" s="26" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>(4) 조회된 버전 정보의 상태가 "사용" 상태인지
 → 사용상태면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="E14" s="20" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>InMemoryServiceMetadataRepository.java</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="F14" s="21" t="inlineStr">
+      <c r="H14" s="25" t="inlineStr">
         <is>
           <t>버전 미사용(INACTIVE)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="16" t="n">
+      <c r="A15" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>서비스/역할 권한 확인</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>(1) 테이블 BS_CLIENT_SERVICE 의 PK 인 (client_id, service_id) 가 (X-Client-ID Header 값, 요청 serviceId) 와
 같은 데이터가 있는지 체크하고, 있으면 해당 데이터의 active_yn 컬럼값이 'Y' 인지 체크한다.
 → 'Y' 이면 (2) 단계 진행</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>AuthorizationService
 authorize(ServiceContext,
             ServiceMetadata)</t>
         </is>
       </c>
-      <c r="E15" s="20" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>DummyAuthorizationService.java</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-003
 HTTP 403</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="H15" s="25" t="inlineStr">
         <is>
           <t>Client 호출 허용 미등록
 Client 호출 차단</t>
@@ -989,9 +1123,9 @@
       </c>
     </row>
     <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="22" t="n"/>
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="A16" s="26" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>(2) 테이블 BS_SERVICE_ROLE 의 PK 인 (service_id, role_code) 에서 요청 serviceId 의 필요 권한 코드
 (화면ID:액션) 를 조회하고, 기존 IFRS17 권한정보(외부 권한 API)의 사용자 화면권한(Y/N) 과
@@ -999,7 +1133,12 @@
 → 모두 'Y' 이면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>AuthorizationService
 authorize(ServiceContext,
@@ -1007,13 +1146,19 @@
 + 기존 IFRS17 권한 API</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>DummyAuthorizationService.java
+(신규) 권한 API 연동 Adapter</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-003
 HTTP 403</t>
         </is>
       </c>
-      <c r="F16" s="21" t="inlineStr">
+      <c r="H16" s="25" t="inlineStr">
         <is>
           <t>서비스 필요권한 미정의
 사용자 화면권한 없음</t>
@@ -1030,23 +1175,35 @@
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr"/>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
       <c r="E17" s="8" t="inlineStr"/>
       <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="10" t="inlineStr"/>
+      <c r="H17" s="11" t="inlineStr"/>
     </row>
     <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="10" t="n">
+      <c r="A18" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="11" t="inlineStr">
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>감사 시작 로그 기록</t>
         </is>
       </c>
-      <c r="C18" s="12" t="inlineStr"/>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="14" t="inlineStr"/>
-      <c r="F18" s="15" t="inlineStr"/>
+      <c r="C18" s="14" t="inlineStr"/>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr"/>
+      <c r="F18" s="16" t="inlineStr"/>
+      <c r="G18" s="17" t="inlineStr"/>
+      <c r="H18" s="18" t="inlineStr"/>
     </row>
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="4" t="n">
@@ -1058,23 +1215,35 @@
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="10" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="10" t="n">
+      <c r="A20" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Legacy Adapter를 통한 기존 Service 호출</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr"/>
-      <c r="D20" s="13" t="inlineStr"/>
-      <c r="E20" s="14" t="inlineStr"/>
-      <c r="F20" s="15" t="inlineStr"/>
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E20" s="15" t="inlineStr"/>
+      <c r="F20" s="16" t="inlineStr"/>
+      <c r="G20" s="17" t="inlineStr"/>
+      <c r="H20" s="18" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="4" t="n">
@@ -1086,23 +1255,35 @@
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="10" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>감사 성공/실패 로그 기록</t>
         </is>
       </c>
-      <c r="C22" s="12" t="inlineStr"/>
-      <c r="D22" s="13" t="inlineStr"/>
-      <c r="E22" s="14" t="inlineStr"/>
-      <c r="F22" s="15" t="inlineStr"/>
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="inlineStr"/>
+      <c r="F22" s="16" t="inlineStr"/>
+      <c r="G22" s="17" t="inlineStr"/>
+      <c r="H22" s="18" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="4" t="n">
@@ -1114,360 +1295,406 @@
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
       <c r="E23" s="8" t="inlineStr"/>
       <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="10" t="inlineStr"/>
+      <c r="H23" s="11" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>기입 근거</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="30" t="inlineStr">
         <is>
           <t>설계서 근거</t>
         </is>
       </c>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="27" t="n"/>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+      <c r="E26" s="31" t="n"/>
+      <c r="F26" s="31" t="n"/>
+      <c r="G26" s="31" t="n"/>
+      <c r="H26" s="32" t="n"/>
     </row>
     <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>3단계 · 담당 컴포넌트</t>
         </is>
       </c>
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>4.2 핵심 컴포넌트 — RequestContextResolver | SSO/Client/Request ID/Trace 정보 생성   /   10.4 공통 Executor 의사코드 — resolveContext → validateClient</t>
         </is>
       </c>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="27" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
+      <c r="H27" s="32" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="28" t="inlineStr">
+      <c r="A28" s="33" t="inlineStr">
         <is>
           <t>3단계 · 오류코드</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   ·   BS-AUTH-001 | 401 | 인증 실패   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001   ·   인증 실패 | 401 | BS-AUTH-001 | SSO/Client 인증 실패   /   5.2 필수 Header — X-Client-ID | Y | 호출 채널 식별</t>
         </is>
       </c>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="27" t="n"/>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+      <c r="E28" s="31" t="n"/>
+      <c r="F28" s="31" t="n"/>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="32" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="28" t="inlineStr">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>3단계 · 참조 데이터</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>테이블 설계서 BS_CLIENT (business_service.bs_client, PK client_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용), "N이면 인증 차단" [핵심 로직]</t>
         </is>
       </c>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="26" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="27" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
+      <c r="H29" s="32" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
+      <c r="A30" s="33" t="inlineStr">
         <is>
           <t>5단계 · 담당 컴포넌트</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>4.2 핵심 컴포넌트 — ServiceMetadataRepository | 서비스 버전·상태·권한·Timeout 조회 | findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="27" t="n"/>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="32" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>5단계 · 오류코드</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>부록 A 표준 오류코드 — BS-SVC-404 | 404 | 서비스/버전 없음 또는 비활성   /   4.5 예외 처리 기준 — 서비스 없음/비활성 | 404 | BS-SVC-404 | Catalog 상태 확인</t>
         </is>
       </c>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="27" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
+      <c r="H31" s="32" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="28" t="inlineStr">
+      <c r="A32" s="33" t="inlineStr">
         <is>
           <t>5단계 · 참조 데이터</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>테이블 설계서 BS_SERVICE (PK service_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용) [핵심 로직]   /   BS_SERVICE_VERSION (PK service_id + version) — status_code varchar(20) DEFAULT 'ACTIVE', ACTIVE(활성)/INACTIVE(비활성), "활성 버전만 실행" [핵심 로직]</t>
         </is>
       </c>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="27" t="n"/>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+      <c r="E32" s="31" t="n"/>
+      <c r="F32" s="31" t="n"/>
+      <c r="G32" s="31" t="n"/>
+      <c r="H32" s="32" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="28" t="inlineStr">
+      <c r="A33" s="33" t="inlineStr">
         <is>
           <t>5단계 (2) 즉시 차단</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>8.4 서비스 등록 및 외부 공개 흐름 7항 — 사용 여부를 "미사용"으로 변경하면 즉시 신규 호출을 차단한다</t>
         </is>
       </c>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="27" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="31" t="n"/>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="31" t="n"/>
+      <c r="H33" s="32" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
+      <c r="A34" s="33" t="inlineStr">
         <is>
           <t>6단계 · 담당 컴포넌트</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>10.4 공통 Executor 의사코드 — authorizeService   /   4.4 표준 인터페이스 — BusinessServiceHandler.authorize(context, request) (업무 파라미터 단위 추가 권한)</t>
         </is>
       </c>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="27" t="n"/>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+      <c r="E34" s="31" t="n"/>
+      <c r="F34" s="31" t="n"/>
+      <c r="G34" s="31" t="n"/>
+      <c r="H34" s="32" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="28" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>6단계 · 오류코드</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>부록 A 표준 오류코드 — BS-AUTH-003 | 403 | 서비스 권한 없음   /   4.5 예외 처리 기준 — 권한 없음 | 403 | BS-AUTH-003 | 서비스 ID와 사용자 정보 감사   /   11.2 필수 인수 시나리오 — 권한 없음 | 유효 사용자, 역할 없음 | 403/BS-AUTH-003</t>
         </is>
       </c>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="27" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
+      <c r="H35" s="32" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
+      <c r="A36" s="33" t="inlineStr">
         <is>
           <t>6단계 · 참조 데이터</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>테이블 설계서 BS_CLIENT_SERVICE (PK client_id + service_id) — active_yn char(1) DEFAULT 'Y', Y(허용)/N(차단), "호출 허용 여부" [핵심 로직]   /   BS_SERVICE_ROLE (PK service_id + role_code) — role_code varchar(100), 화면ID:액션 형식, 화면ID=[A-Z]{4}M[0-9]{3}, 액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력), 예) CLSGM001:inqy</t>
         </is>
       </c>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="27" t="n"/>
+      <c r="C36" s="31" t="n"/>
+      <c r="D36" s="31" t="n"/>
+      <c r="E36" s="31" t="n"/>
+      <c r="F36" s="31" t="n"/>
+      <c r="G36" s="31" t="n"/>
+      <c r="H36" s="32" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="33" t="inlineStr">
         <is>
           <t>6단계 · 권한 원칙</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>6.2 권한 원칙 — 서비스 권한은 BS_SERVICE_ROLE 과 기존 IFRS17 권한정보를 함께 사용한다   /   테이블 설계서 BS_SERVICE_ROLE 설명 — "외부 권한API의 사용자 화면권한(Y/N)과 AND 비교(§6.2 권한 원칙)"</t>
         </is>
       </c>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="26" t="n"/>
-      <c r="E37" s="26" t="n"/>
-      <c r="F37" s="27" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="32" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="30" t="inlineStr">
+      <c r="A39" s="34" t="inlineStr">
+        <is>
+          <t>※ [공통] 현황은 이번 업무의뢰의 구현 대상 여부와 진행 상태를 표기한다. 예정 = 구현 진행 예정, 완료 = 구현 진행 완료, 미대상 = 이번 구현 범위가 아님. 4단계 SSO 사용자 Context 추출은 이번 구현 대상이 아니므로 미대상으로 표기한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="34" t="inlineStr">
+        <is>
+          <t>※ [공통] 수정 대상은 소스코드를 추가 작성·수정해야 하는 파일이다. Interface 파일(RequestContextResolver.java 등)은 선언부만 보유하므로 수정 대상이 아니며, 해당 Interface 를 implements 한 구현체 클래스 파일을 기재한다. 경로는 src/main/java/com/koreanre/ifrs17/businessservice 하위이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="34" t="inlineStr">
         <is>
           <t>※ [공통] 참조 데이터의 테이블·컬럼·유효값은 별도 [테이블 설계서] (business_service Schema, PostgreSQL) 를 기준으로 한다.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="30" t="inlineStr">
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="34" t="inlineStr">
         <is>
           <t>※ [공통] 오류코드명은 동일 오류코드 안에서 실패 원인을 구분하기 위한 표기이며, 외부 응답의 message 문구는 구현 시 확정한다.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="30" t="inlineStr">
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="34" t="inlineStr">
         <is>
           <t>※ [공통] 담당 컴포넌트는 Interface 기준 표기이다. 선언부는 Interface 에, 실제 로직은 구현체 클래스에 작성한다. 현행 구현체 : RequestContextResolver→HttpHeaderRequestContextResolver, ClientAuthenticationService→DummyClientAuthenticationService, ServiceMetadataRepository→InMemoryServiceMetadataRepository, AuthorizationService→DummyAuthorizationService. Dummy·InMemory 구현체는 DB 연동 시 교체 대상이다.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="30" t="inlineStr">
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="34" t="inlineStr">
         <is>
           <t>※ [3단계] 호출 Client 검증 단계에서는 BS_CLIENT 테이블만 조회하며, BS_CLIENT_SERVICE 테이블에는 접근하지 않는다.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="30" t="inlineStr">
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="34" t="inlineStr">
         <is>
           <t>※ [3단계] 세부 단계 (2) 는 BS_CLIENT 등록 여부와 active_yn = 'Y' 를 하나의 단계에서 판정하며, 두 경우 모두 부록 A 의 BS-AUTH-001(401) 로 처리한다. 미등록과 비활성은 응답 오류코드로 구분되지 않으며, 오류코드명과 감사 로그로 식별한다.</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="30" t="inlineStr">
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="34" t="inlineStr">
         <is>
           <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="30" t="inlineStr">
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="34" t="inlineStr">
         <is>
           <t>※ [5단계] 세부 단계 (2) 는 BS_SERVICE.active_yn = 'Y', (4) 는 BS_SERVICE_VERSION.status_code = 'ACTIVE' 를 판정한다. 두 테이블의 상태 컬럼명이 서로 다른 점에 유의한다.</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="30" t="inlineStr">
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="34" t="inlineStr">
         <is>
           <t>※ [6단계] 세부 단계 (2) 는 BS_SERVICE_ROLE 에 active_yn 컬럼이 없으므로 상태값을 판정하지 않는다. 테이블 설계서의 BS_SERVICE_ROLE 정의에 따라 필요 권한 코드(화면ID:액션) 존재 여부와 외부 권한 API 의 사용자 화면권한(Y/N) 을 AND 비교하여 판정한다.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="30" t="inlineStr">
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="34" t="inlineStr">
         <is>
           <t>※ [6단계] role_code 의 액션은 inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력) 5종이나, Phase 1 의 REST API 는 조회만 수행하므로 inqy 로 고정된다. 따라서 사용자 권한과 서비스 권한의 다대다 대조는 발생하지 않는다.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="A48" s="30" t="inlineStr">
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="34" t="inlineStr">
         <is>
           <t>※ [6단계] 사용자 화면권한은 기존 IFRS17 권한 테이블을 Join 하여 취득하는 값이므로 Request 입력 항목이 아니다.</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="26" customHeight="1">
-      <c r="A49" s="30" t="inlineStr">
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="34" t="inlineStr">
         <is>
           <t>※ [6단계] 담당 컴포넌트 AuthorizationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 authorizeService 단계를 담당할 컴포넌트로 명명한 것이다.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
-      <c r="A50" s="30" t="inlineStr">
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="34" t="inlineStr">
         <is>
           <t>※ 각 단계의 DB 접속 실패 등 인프라 오류는 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="34" t="inlineStr">
         <is>
           <t>※ 예외 처리 절차(예외 클래스·실패 감사 로그·표준 Error Response 조립)는 기능 관점의 본 표와 성격이 달라 제외하였으며, 구현 착수 시점에 별도 표로 작성한다.</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="30" t="inlineStr">
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="34" t="inlineStr">
         <is>
           <t>※ [7단계 상세화 시 반영] 업무 파라미터 기반 추가 권한 확인을 포함한다. 근거 : 6.1 인증과 권한 흐름 5항 / 4.4 표준 인터페이스 BusinessServiceHandler.authorize(context, request).</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="26" customHeight="1">
-      <c r="A53" s="30" t="inlineStr">
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="34" t="inlineStr">
         <is>
           <t>※ [12단계 상세화 시 반영] 최종 허용/거부 결과의 감사 기록(authorization_result) 을 포함한다. 근거 : 6.1 인증과 권한 흐름 6항 / 6.3 감사로그 필수항목 — 보안 | remote_ip, auth_type, authorization_result.</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="26" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="34" t="inlineStr">
         <is>
           <t>※ 1~2 · 4 · 7~13 단계의 세부 단계·담당 컴포넌트·오류코드·오류코드명은 후속 상세화 시 기입한다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="37">
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="A54:F54"/>
-    <mergeCell ref="A46:F46"/>
+  <mergeCells count="39">
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A51:H51"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B30:H30"/>
     <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="B33:H33"/>
     <mergeCell ref="B11:B14"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="B27:F27"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="B37:H37"/>
+    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="B31:H31"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A52:F52"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A52:H52"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="B34:H34"/>
+    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -703,7 +703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1165,180 +1165,224 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="24" customHeight="1">
-      <c r="A17" s="4" t="n">
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>입력 Schema 및 업무 파라미터 검증</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr"/>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>(1) 테이블 BS_SERVICE_PARAM 의 PK 인 (service_id, version, param_name) 로 요청 serviceId 와 확정 version 의
+파라미터 정의 목록을 조회하고, 필수 파라미터가 Request 의 parameters 에 모두 입력되었는지 체크한다.
+→ 모두 입력되어 있으면 (2) 단계 진행</t>
+        </is>
+      </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr"/>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="12" t="n">
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>StandardRequestValidator
+validate(StandardRequest,
+           ServiceMetadata)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>StandardRequestValidator.java</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>BS-VAL-001
+HTTP 400</t>
+        </is>
+      </c>
+      <c r="H17" s="25" t="inlineStr">
+        <is>
+          <t>필수 파라미터 미입력</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>(2) 검증을 통과한 parameters 를 서비스별 요청 DTO 로 바인딩한다.
+→ 바인딩에 성공하면 다음 프로세스 진행</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>ParameterBinder
+bind(parameters, requestType)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>ParameterBinder.java</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>BS-VAL-001
+HTTP 400</t>
+        </is>
+      </c>
+      <c r="H18" s="25" t="inlineStr">
+        <is>
+          <t>DTO 바인딩 실패</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>감사 시작 로그 기록</t>
         </is>
       </c>
-      <c r="C18" s="14" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="C19" s="14" t="inlineStr"/>
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr"/>
-      <c r="F18" s="16" t="inlineStr"/>
-      <c r="G18" s="17" t="inlineStr"/>
-      <c r="H18" s="18" t="inlineStr"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="4" t="n">
+      <c r="E19" s="15" t="inlineStr"/>
+      <c r="F19" s="16" t="inlineStr"/>
+      <c r="G19" s="17" t="inlineStr"/>
+      <c r="H19" s="18" t="inlineStr"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Business Service Handler 실행</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr"/>
-      <c r="F19" s="9" t="inlineStr"/>
-      <c r="G19" s="10" t="inlineStr"/>
-      <c r="H19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="12" t="n">
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="10" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B20" s="13" t="inlineStr">
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>Legacy Adapter를 통한 기존 Service 호출</t>
         </is>
       </c>
-      <c r="C20" s="14" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C21" s="14" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr"/>
-      <c r="F20" s="16" t="inlineStr"/>
-      <c r="G20" s="17" t="inlineStr"/>
-      <c r="H20" s="18" t="inlineStr"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="4" t="n">
+      <c r="E21" s="15" t="inlineStr"/>
+      <c r="F21" s="16" t="inlineStr"/>
+      <c r="G21" s="17" t="inlineStr"/>
+      <c r="H21" s="18" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>결과 DTO를 표준 JSON으로 변환 및 마스킹</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
-      <c r="G21" s="10" t="inlineStr"/>
-      <c r="H21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="12" t="n">
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="10" t="inlineStr"/>
+      <c r="H22" s="11" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B22" s="13" t="inlineStr">
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>감사 성공/실패 로그 기록</t>
         </is>
       </c>
-      <c r="C22" s="14" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C23" s="14" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr"/>
-      <c r="F22" s="16" t="inlineStr"/>
-      <c r="G22" s="17" t="inlineStr"/>
-      <c r="H22" s="18" t="inlineStr"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="4" t="n">
+      <c r="E23" s="15" t="inlineStr"/>
+      <c r="F23" s="16" t="inlineStr"/>
+      <c r="G23" s="17" t="inlineStr"/>
+      <c r="H23" s="18" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>표준 Response 반환</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
-      <c r="G23" s="10" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr"/>
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="10" t="inlineStr"/>
+      <c r="H24" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="29" t="inlineStr">
         <is>
           <t>기입 근거</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="30" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B27" s="30" t="inlineStr">
         <is>
           <t>설계서 근거</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="n"/>
-      <c r="D26" s="31" t="n"/>
-      <c r="E26" s="31" t="n"/>
-      <c r="F26" s="31" t="n"/>
-      <c r="G26" s="31" t="n"/>
-      <c r="H26" s="32" t="n"/>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="33" t="inlineStr">
-        <is>
-          <t>3단계 · 담당 컴포넌트</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>4.2 핵심 컴포넌트 — RequestContextResolver | SSO/Client/Request ID/Trace 정보 생성   /   10.4 공통 Executor 의사코드 — resolveContext → validateClient</t>
         </is>
       </c>
       <c r="C27" s="31" t="n"/>
@@ -1351,12 +1395,12 @@
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="33" t="inlineStr">
         <is>
-          <t>3단계 · 오류코드</t>
+          <t>3단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   ·   BS-AUTH-001 | 401 | 인증 실패   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001   ·   인증 실패 | 401 | BS-AUTH-001 | SSO/Client 인증 실패   /   5.2 필수 Header — X-Client-ID | Y | 호출 채널 식별</t>
+          <t>4.2 핵심 컴포넌트 — RequestContextResolver | SSO/Client/Request ID/Trace 정보 생성   /   10.4 공통 Executor 의사코드 — resolveContext → validateClient</t>
         </is>
       </c>
       <c r="C28" s="31" t="n"/>
@@ -1369,12 +1413,12 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="33" t="inlineStr">
         <is>
-          <t>3단계 · 참조 데이터</t>
+          <t>3단계 · 오류코드</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_CLIENT (business_service.bs_client, PK client_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용), "N이면 인증 차단" [핵심 로직]</t>
+          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   ·   BS-AUTH-001 | 401 | 인증 실패   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001   ·   인증 실패 | 401 | BS-AUTH-001 | SSO/Client 인증 실패   /   5.2 필수 Header — X-Client-ID | Y | 호출 채널 식별</t>
         </is>
       </c>
       <c r="C29" s="31" t="n"/>
@@ -1387,12 +1431,12 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>5단계 · 담당 컴포넌트</t>
+          <t>3단계 · 참조 데이터</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>4.2 핵심 컴포넌트 — ServiceMetadataRepository | 서비스 버전·상태·권한·Timeout 조회 | findActive(serviceId, version)</t>
+          <t>테이블 설계서 BS_CLIENT (business_service.bs_client, PK client_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용), "N이면 인증 차단" [핵심 로직]</t>
         </is>
       </c>
       <c r="C30" s="31" t="n"/>
@@ -1405,12 +1449,12 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>5단계 · 오류코드</t>
+          <t>5단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-SVC-404 | 404 | 서비스/버전 없음 또는 비활성   /   4.5 예외 처리 기준 — 서비스 없음/비활성 | 404 | BS-SVC-404 | Catalog 상태 확인</t>
+          <t>4.2 핵심 컴포넌트 — ServiceMetadataRepository | 서비스 버전·상태·권한·Timeout 조회 | findActive(serviceId, version)</t>
         </is>
       </c>
       <c r="C31" s="31" t="n"/>
@@ -1423,12 +1467,12 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>5단계 · 참조 데이터</t>
+          <t>5단계 · 오류코드</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_SERVICE (PK service_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용) [핵심 로직]   /   BS_SERVICE_VERSION (PK service_id + version) — status_code varchar(20) DEFAULT 'ACTIVE', ACTIVE(활성)/INACTIVE(비활성), "활성 버전만 실행" [핵심 로직]</t>
+          <t>부록 A 표준 오류코드 — BS-SVC-404 | 404 | 서비스/버전 없음 또는 비활성   /   4.5 예외 처리 기준 — 서비스 없음/비활성 | 404 | BS-SVC-404 | Catalog 상태 확인</t>
         </is>
       </c>
       <c r="C32" s="31" t="n"/>
@@ -1441,12 +1485,12 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="33" t="inlineStr">
         <is>
-          <t>5단계 (2) 즉시 차단</t>
+          <t>5단계 · 참조 데이터</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>8.4 서비스 등록 및 외부 공개 흐름 7항 — 사용 여부를 "미사용"으로 변경하면 즉시 신규 호출을 차단한다</t>
+          <t>테이블 설계서 BS_SERVICE (PK service_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용) [핵심 로직]   /   BS_SERVICE_VERSION (PK service_id + version) — status_code varchar(20) DEFAULT 'ACTIVE', ACTIVE(활성)/INACTIVE(비활성), "활성 버전만 실행" [핵심 로직]</t>
         </is>
       </c>
       <c r="C33" s="31" t="n"/>
@@ -1459,12 +1503,12 @@
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 담당 컴포넌트</t>
+          <t>5단계 (2) 즉시 차단</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>10.4 공통 Executor 의사코드 — authorizeService   /   4.4 표준 인터페이스 — BusinessServiceHandler.authorize(context, request) (업무 파라미터 단위 추가 권한)</t>
+          <t>8.4 서비스 등록 및 외부 공개 흐름 7항 — 사용 여부를 "미사용"으로 변경하면 즉시 신규 호출을 차단한다</t>
         </is>
       </c>
       <c r="C34" s="31" t="n"/>
@@ -1477,12 +1521,12 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 오류코드</t>
+          <t>6단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-AUTH-003 | 403 | 서비스 권한 없음   /   4.5 예외 처리 기준 — 권한 없음 | 403 | BS-AUTH-003 | 서비스 ID와 사용자 정보 감사   /   11.2 필수 인수 시나리오 — 권한 없음 | 유효 사용자, 역할 없음 | 403/BS-AUTH-003</t>
+          <t>10.4 공통 Executor 의사코드 — authorizeService   /   4.4 표준 인터페이스 — BusinessServiceHandler.authorize(context, request) (업무 파라미터 단위 추가 권한)</t>
         </is>
       </c>
       <c r="C35" s="31" t="n"/>
@@ -1495,12 +1539,12 @@
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 참조 데이터</t>
+          <t>6단계 · 오류코드</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_CLIENT_SERVICE (PK client_id + service_id) — active_yn char(1) DEFAULT 'Y', Y(허용)/N(차단), "호출 허용 여부" [핵심 로직]   /   BS_SERVICE_ROLE (PK service_id + role_code) — role_code varchar(100), 화면ID:액션 형식, 화면ID=[A-Z]{4}M[0-9]{3}, 액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력), 예) CLSGM001:inqy</t>
+          <t>부록 A 표준 오류코드 — BS-AUTH-003 | 403 | 서비스 권한 없음   /   4.5 예외 처리 기준 — 권한 없음 | 403 | BS-AUTH-003 | 서비스 ID와 사용자 정보 감사   /   11.2 필수 인수 시나리오 — 권한 없음 | 유효 사용자, 역할 없음 | 403/BS-AUTH-003</t>
         </is>
       </c>
       <c r="C36" s="31" t="n"/>
@@ -1513,12 +1557,12 @@
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 권한 원칙</t>
+          <t>6단계 · 참조 데이터</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>6.2 권한 원칙 — 서비스 권한은 BS_SERVICE_ROLE 과 기존 IFRS17 권한정보를 함께 사용한다   /   테이블 설계서 BS_SERVICE_ROLE 설명 — "외부 권한API의 사용자 화면권한(Y/N)과 AND 비교(§6.2 권한 원칙)"</t>
+          <t>테이블 설계서 BS_CLIENT_SERVICE (PK client_id + service_id) — active_yn char(1) DEFAULT 'Y', Y(허용)/N(차단), "호출 허용 여부" [핵심 로직]   /   BS_SERVICE_ROLE (PK service_id + role_code) — role_code varchar(100), 화면ID:액션 형식, 화면ID=[A-Z]{4}M[0-9]{3}, 액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력), 예) CLSGM001:inqy</t>
         </is>
       </c>
       <c r="C37" s="31" t="n"/>
@@ -1528,137 +1572,241 @@
       <c r="G37" s="31" t="n"/>
       <c r="H37" s="32" t="n"/>
     </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="33" t="inlineStr">
+        <is>
+          <t>7단계 · 담당 컴포넌트</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>4.3-12 입력 Schema 및 업무 파라미터 검증   /   10.4 공통 Executor 의사코드 — authorizeService 이후 invokeHandler 이전   /   현행 코드 StandardRequestValidator.validate(StandardRequest, ServiceMetadata) · ParameterBinder.bind(Map, Class)</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="n"/>
+      <c r="D38" s="31" t="n"/>
+      <c r="E38" s="31" t="n"/>
+      <c r="F38" s="31" t="n"/>
+      <c r="G38" s="31" t="n"/>
+      <c r="H38" s="32" t="n"/>
+    </row>
     <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 현황은 이번 업무의뢰의 구현 대상 여부와 진행 상태를 표기한다. 예정 = 구현 진행 예정, 완료 = 구현 진행 완료, 미대상 = 이번 구현 범위가 아님. 4단계 SSO 사용자 Context 추출은 이번 구현 대상이 아니므로 미대상으로 표기한다.</t>
-        </is>
-      </c>
+      <c r="A39" s="33" t="inlineStr">
+        <is>
+          <t>7단계 · 오류코드</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001 | 필드별 오류 반환, Stack Trace 금지   /   11.2 필수 인수 시나리오 — 입력 오류 | 잘못된 YYYY-MM | 400/BS-VAL-001</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="32" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1">
-      <c r="A40" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 수정 대상은 소스코드를 추가 작성·수정해야 하는 파일이다. Interface 파일(RequestContextResolver.java 등)은 선언부만 보유하므로 수정 대상이 아니며, 해당 Interface 를 implements 한 구현체 클래스 파일을 기재한다. 경로는 src/main/java/com/koreanre/ifrs17/businessservice 하위이다.</t>
-        </is>
-      </c>
+      <c r="A40" s="33" t="inlineStr">
+        <is>
+          <t>7단계 · 참조 데이터</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>7.2 주요 테이블 — BS_SERVICE_PARAM | 입력 파라미터 정의 | service_id, version, param_name (테이블 설계서 시트 미확인)</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="n"/>
+      <c r="D40" s="31" t="n"/>
+      <c r="E40" s="31" t="n"/>
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="32" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 참조 데이터의 테이블·컬럼·유효값은 별도 [테이블 설계서] (business_service Schema, PostgreSQL) 를 기준으로 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="26" customHeight="1">
-      <c r="A42" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 오류코드명은 동일 오류코드 안에서 실패 원인을 구분하기 위한 표기이며, 외부 응답의 message 문구는 구현 시 확정한다.</t>
-        </is>
-      </c>
+      <c r="A41" s="33" t="inlineStr">
+        <is>
+          <t>6단계 · 권한 원칙</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>6.2 권한 원칙 — 서비스 권한은 BS_SERVICE_ROLE 과 기존 IFRS17 권한정보를 함께 사용한다   /   테이블 설계서 BS_SERVICE_ROLE 설명 — "외부 권한API의 사용자 화면권한(Y/N)과 AND 비교(§6.2 권한 원칙)"</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="31" t="n"/>
+      <c r="F41" s="31" t="n"/>
+      <c r="G41" s="31" t="n"/>
+      <c r="H41" s="32" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="34" t="inlineStr">
         <is>
-          <t>※ [공통] 담당 컴포넌트는 Interface 기준 표기이다. 선언부는 Interface 에, 실제 로직은 구현체 클래스에 작성한다. 현행 구현체 : RequestContextResolver→HttpHeaderRequestContextResolver, ClientAuthenticationService→DummyClientAuthenticationService, ServiceMetadataRepository→InMemoryServiceMetadataRepository, AuthorizationService→DummyAuthorizationService. Dummy·InMemory 구현체는 DB 연동 시 교체 대상이다.</t>
+          <t>※ [공통] 현황은 이번 업무의뢰의 구현 대상 여부와 진행 상태를 표기한다. 예정 = 구현 진행 예정, 완료 = 구현 진행 완료, 미대상 = 이번 구현 범위가 아님. 4단계 SSO 사용자 Context 추출은 이번 구현 대상이 아니므로 미대상으로 표기한다.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 호출 Client 검증 단계에서는 BS_CLIENT 테이블만 조회하며, BS_CLIENT_SERVICE 테이블에는 접근하지 않는다.</t>
+          <t>※ [공통] 수정 대상은 소스코드를 추가 작성·수정해야 하는 파일이다. Interface 파일(RequestContextResolver.java 등)은 선언부만 보유하므로 수정 대상이 아니며, 해당 Interface 를 implements 한 구현체 클래스 파일을 기재한다. 경로는 src/main/java/com/koreanre/ifrs17/businessservice 하위이다.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 세부 단계 (2) 는 BS_CLIENT 등록 여부와 active_yn = 'Y' 를 하나의 단계에서 판정하며, 두 경우 모두 부록 A 의 BS-AUTH-001(401) 로 처리한다. 미등록과 비활성은 응답 오류코드로 구분되지 않으며, 오류코드명과 감사 로그로 식별한다.</t>
+          <t>※ [공통] 참조 데이터의 테이블·컬럼·유효값은 별도 [테이블 설계서] (business_service Schema, PostgreSQL) 를 기준으로 한다.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+          <t>※ [공통] 오류코드명은 동일 오류코드 안에서 실패 원인을 구분하기 위한 표기이며, 외부 응답의 message 문구는 구현 시 확정한다.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="34" t="inlineStr">
         <is>
-          <t>※ [5단계] 세부 단계 (2) 는 BS_SERVICE.active_yn = 'Y', (4) 는 BS_SERVICE_VERSION.status_code = 'ACTIVE' 를 판정한다. 두 테이블의 상태 컬럼명이 서로 다른 점에 유의한다.</t>
+          <t>※ [공통] 담당 컴포넌트는 Interface 기준 표기이다. 선언부는 Interface 에, 실제 로직은 구현체 클래스에 작성한다. 현행 구현체 : RequestContextResolver→HttpHeaderRequestContextResolver, ClientAuthenticationService→DummyClientAuthenticationService, ServiceMetadataRepository→InMemoryServiceMetadataRepository, AuthorizationService→DummyAuthorizationService. Dummy·InMemory 구현체는 DB 연동 시 교체 대상이다.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 세부 단계 (2) 는 BS_SERVICE_ROLE 에 active_yn 컬럼이 없으므로 상태값을 판정하지 않는다. 테이블 설계서의 BS_SERVICE_ROLE 정의에 따라 필요 권한 코드(화면ID:액션) 존재 여부와 외부 권한 API 의 사용자 화면권한(Y/N) 을 AND 비교하여 판정한다.</t>
+          <t>※ [3단계] 호출 Client 검증 단계에서는 BS_CLIENT 테이블만 조회하며, BS_CLIENT_SERVICE 테이블에는 접근하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] role_code 의 액션은 inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력) 5종이나, Phase 1 의 REST API 는 조회만 수행하므로 inqy 로 고정된다. 따라서 사용자 권한과 서비스 권한의 다대다 대조는 발생하지 않는다.</t>
+          <t>※ [3단계] 세부 단계 (2) 는 BS_CLIENT 등록 여부와 active_yn = 'Y' 를 하나의 단계에서 판정하며, 두 경우 모두 부록 A 의 BS-AUTH-001(401) 로 처리한다. 미등록과 비활성은 응답 오류코드로 구분되지 않으며, 오류코드명과 감사 로그로 식별한다.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 사용자 화면권한은 기존 IFRS17 권한 테이블을 Join 하여 취득하는 값이므로 Request 입력 항목이 아니다.</t>
+          <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 담당 컴포넌트 AuthorizationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 authorizeService 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+          <t>※ [5단계] 세부 단계 (2) 는 BS_SERVICE.active_yn = 'Y', (4) 는 BS_SERVICE_VERSION.status_code = 'ACTIVE' 를 판정한다. 두 테이블의 상태 컬럼명이 서로 다른 점에 유의한다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="34" t="inlineStr">
         <is>
-          <t>※ 각 단계의 DB 접속 실패 등 인프라 오류는 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
+          <t>※ [6단계] 세부 단계 (2) 는 BS_SERVICE_ROLE 에 active_yn 컬럼이 없으므로 상태값을 판정하지 않는다. 테이블 설계서의 BS_SERVICE_ROLE 정의에 따라 필요 권한 코드(화면ID:액션) 존재 여부와 외부 권한 API 의 사용자 화면권한(Y/N) 을 AND 비교하여 판정한다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="34" t="inlineStr">
         <is>
-          <t>※ 예외 처리 절차(예외 클래스·실패 감사 로그·표준 Error Response 조립)는 기능 관점의 본 표와 성격이 달라 제외하였으며, 구현 착수 시점에 별도 표로 작성한다.</t>
+          <t>※ [6단계] role_code 의 액션은 inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력) 5종이나, Phase 1 의 REST API 는 조회만 수행하므로 inqy 로 고정된다. 따라서 사용자 권한과 서비스 권한의 다대다 대조는 발생하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계 상세화 시 반영] 업무 파라미터 기반 추가 권한 확인을 포함한다. 근거 : 6.1 인증과 권한 흐름 5항 / 4.4 표준 인터페이스 BusinessServiceHandler.authorize(context, request).</t>
+          <t>※ [6단계] 사용자 화면권한은 기존 IFRS17 권한 테이블을 Join 하여 취득하는 값이므로 Request 입력 항목이 아니다.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="34" t="inlineStr">
         <is>
-          <t>※ [12단계 상세화 시 반영] 최종 허용/거부 결과의 감사 기록(authorization_result) 을 포함한다. 근거 : 6.1 인증과 권한 흐름 6항 / 6.3 감사로그 필수항목 — 보안 | remote_ip, auth_type, authorization_result.</t>
+          <t>※ [6단계] 담당 컴포넌트 AuthorizationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 authorizeService 단계를 담당할 컴포넌트로 명명한 것이다.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>※ 1~2 · 4 · 7~13 단계의 세부 단계·담당 컴포넌트·오류코드·오류코드명은 후속 상세화 시 기입한다.</t>
+          <t>※ [7단계] 파라미터의 데이터 타입·형식 검증은 별도 세부 단계로 두지 않는다. 타입 불일치는 (2) DTO 바인딩 시 변환 실패로 걸러지므로 추가 코드가 필요하지 않다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 허용값·허용범위 검증은 이번 구현 범위에서 제외한다. 서비스별 업무 규칙 성격이 강해 공통 단계에서 테이블 기반으로 일반화하면 코드량이 커지며, 설계서 10.2 예시와 같이 BusinessServiceHandler.validate() 에서 서비스별로 처리한다. 이에 따라 부록 A 의 BS-VAL-002(허용범위 초과)는 이번 구현 범위에서 발생 지점이 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 검증 기준 데이터는 BS_SERVICE_PARAM 을 사용한다. BS_SERVICE_VERSION.request_schema 는 5단계 Service Catalog 활성 버전 조회의 대상 테이블 컬럼이므로 7단계 판정에는 사용하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 업무 파라미터 기반 추가 권한 확인(6.1 인증과 권한 흐름 5항)은 이번 구현 범위에서 제외한다. 사용자 권한 판정은 4단계 사용자 Context 와 6단계 서비스/역할 권한 확인에서 종결되며, Phase 1 조회 서비스의 파라미터(기준년월·회계기준·보고서유형 등)에는 사용자별 접근 범위를 가르는 식별자가 없다. 설계서 10.2 예시도 해당 확인을 "필요 시" 조건부로 기술한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] BS_SERVICE_PARAM 은 테이블 설계서 시트를 확인하지 못했다. 필수 여부 컬럼명은 시트 확인 후 확정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="34" t="inlineStr">
+        <is>
+          <t>※ 각 단계의 DB 접속 실패 등 인프라 오류는 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="34" t="inlineStr">
+        <is>
+          <t>※ 예외 처리 절차(예외 클래스·실패 감사 로그·표준 Error Response 조립)는 기능 관점의 본 표와 성격이 달라 제외하였으며, 구현 착수 시점에 별도 표로 작성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="34" t="inlineStr">
+        <is>
+          <t>※ [12단계 상세화 시 반영] 최종 허용/거부 결과의 감사 기록(authorization_result) 을 포함한다. 근거 : 6.1 인증과 권한 흐름 6항 / 6.3 감사로그 필수항목 — 보안 | remote_ip, auth_type, authorization_result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="34" t="inlineStr">
+        <is>
+          <t>※ 1~2 · 8~13 단계의 세부 단계·현황·담당 컴포넌트·수정 대상·오류코드·오류코드명은 후속 상세화 시 기입한다. 4단계는 이번 구현 미대상이다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="48">
     <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="A59:H59"/>
     <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="A60:H60"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="B30:H30"/>
     <mergeCell ref="A11:A14"/>
@@ -1668,12 +1816,12 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="B37:H37"/>
+    <mergeCell ref="A61:H61"/>
     <mergeCell ref="B36:H36"/>
     <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B26:H26"/>
+    <mergeCell ref="B41:H41"/>
     <mergeCell ref="B35:H35"/>
     <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A41:H41"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="B31:H31"/>
     <mergeCell ref="B15:B16"/>
@@ -1683,18 +1831,23 @@
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A55:H55"/>
     <mergeCell ref="B27:H27"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="B39:H39"/>
     <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A62:H62"/>
     <mergeCell ref="A53:H53"/>
     <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A63:H63"/>
     <mergeCell ref="A52:H52"/>
     <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B38:H38"/>
     <mergeCell ref="B29:H29"/>
     <mergeCell ref="A44:H44"/>
     <mergeCell ref="B34:H34"/>
+    <mergeCell ref="A58:H58"/>
     <mergeCell ref="B28:H28"/>
-    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -703,17 +703,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H64"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -765,15 +766,20 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
+          <t>참조 데이터</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
           <t>수정 대상</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>오류코드</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>오류코드명</t>
         </is>
@@ -795,9 +801,17 @@
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr"/>
-      <c r="H6" s="11" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>[Header] Authorization, X-Request-ID,
+X-Client-ID, X-User-ID, X-Trace-ID,
+Content-Type
+[Body] serviceVersion, parameters, options</t>
+        </is>
+      </c>
+      <c r="G6" s="9" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="11" t="inlineStr"/>
     </row>
     <row r="7" ht="24" customHeight="1">
       <c r="A7" s="12" t="n">
@@ -815,9 +829,14 @@
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr"/>
-      <c r="F7" s="16" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="18" t="inlineStr"/>
+      <c r="F7" s="15" t="inlineStr">
+        <is>
+          <t>[Header] X-Request-ID, X-Trace-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr"/>
+      <c r="H7" s="17" t="inlineStr"/>
+      <c r="I7" s="18" t="inlineStr"/>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="19" t="n">
@@ -846,18 +865,23 @@
           serviceId, request)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>[Header] X-Client-ID</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>HttpHeaderRequestContextResolver.java</t>
         </is>
       </c>
-      <c r="G8" s="24" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>BS-VAL-001
 HTTP 400</t>
         </is>
       </c>
-      <c r="H8" s="25" t="inlineStr">
+      <c r="I8" s="25" t="inlineStr">
         <is>
           <t>Client ID 미입력</t>
         </is>
@@ -884,18 +908,23 @@
 authenticate(ServiceContext)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_CLIENT</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>DummyClientAuthenticationService.java</t>
         </is>
       </c>
-      <c r="G9" s="24" t="inlineStr">
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-001
 HTTP 401</t>
         </is>
       </c>
-      <c r="H9" s="25" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t>미등록 Client
 미사용 Client</t>
@@ -918,9 +947,14 @@
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr"/>
-      <c r="F10" s="16" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="18" t="inlineStr"/>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>[Header] Authorization, X-User-ID</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr"/>
+      <c r="H10" s="17" t="inlineStr"/>
+      <c r="I10" s="18" t="inlineStr"/>
     </row>
     <row r="11" ht="50" customHeight="1">
       <c r="A11" s="19" t="n">
@@ -948,18 +982,23 @@
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_SERVICE</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="G11" s="24" t="inlineStr">
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="H11" s="25" t="inlineStr">
+      <c r="I11" s="25" t="inlineStr">
         <is>
           <t>서비스 미존재</t>
         </is>
@@ -985,18 +1024,23 @@
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_SERVICE</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="G12" s="24" t="inlineStr">
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="H12" s="25" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t>서비스 미사용</t>
         </is>
@@ -1022,18 +1066,23 @@
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_SERVICE_VERSION</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="G13" s="24" t="inlineStr">
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="H13" s="25" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t>버전 미존재</t>
         </is>
@@ -1059,18 +1108,23 @@
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_SERVICE_VERSION</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="G14" s="24" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="H14" s="25" t="inlineStr">
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>버전 미사용(INACTIVE)</t>
         </is>
@@ -1104,18 +1158,23 @@
             ServiceMetadata)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_CLIENT_SERVICE</t>
+        </is>
+      </c>
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>DummyAuthorizationService.java</t>
         </is>
       </c>
-      <c r="G15" s="24" t="inlineStr">
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-003
 HTTP 403</t>
         </is>
       </c>
-      <c r="H15" s="25" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>Client 호출 허용 미등록
 Client 호출 차단</t>
@@ -1146,19 +1205,25 @@
 + 기존 IFRS17 권한 API</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_SERVICE_ROLE
+[API] 기존 IFRS17 권한 API</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>DummyAuthorizationService.java
 (신규) 권한 API 연동 Adapter</t>
         </is>
       </c>
-      <c r="G16" s="24" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-003
 HTTP 403</t>
         </is>
       </c>
-      <c r="H16" s="25" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>서비스 필요권한 미정의
 사용자 화면권한 없음</t>
@@ -1193,18 +1258,23 @@
            ServiceMetadata)</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>[Table] BS_SERVICE_PARAM</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>StandardRequestValidator.java</t>
         </is>
       </c>
-      <c r="G17" s="24" t="inlineStr">
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>BS-VAL-001
 HTTP 400</t>
         </is>
       </c>
-      <c r="H17" s="25" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>필수 파라미터 미입력</t>
         </is>
@@ -1230,18 +1300,23 @@
 bind(parameters, requestType)</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>ParameterBinder.java</t>
         </is>
       </c>
-      <c r="G18" s="24" t="inlineStr">
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>BS-VAL-001
 HTTP 400</t>
         </is>
       </c>
-      <c r="H18" s="25" t="inlineStr">
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t>DTO 바인딩 실패</t>
         </is>
@@ -1263,9 +1338,10 @@
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr"/>
-      <c r="F19" s="16" t="inlineStr"/>
-      <c r="G19" s="17" t="inlineStr"/>
-      <c r="H19" s="18" t="inlineStr"/>
+      <c r="F19" s="15" t="inlineStr"/>
+      <c r="G19" s="16" t="inlineStr"/>
+      <c r="H19" s="17" t="inlineStr"/>
+      <c r="I19" s="18" t="inlineStr"/>
     </row>
     <row r="20" ht="24" customHeight="1">
       <c r="A20" s="4" t="n">
@@ -1283,9 +1359,10 @@
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="9" t="inlineStr"/>
-      <c r="G20" s="10" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr"/>
     </row>
     <row r="21" ht="24" customHeight="1">
       <c r="A21" s="12" t="n">
@@ -1303,9 +1380,10 @@
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr"/>
-      <c r="F21" s="16" t="inlineStr"/>
-      <c r="G21" s="17" t="inlineStr"/>
-      <c r="H21" s="18" t="inlineStr"/>
+      <c r="F21" s="15" t="inlineStr"/>
+      <c r="G21" s="16" t="inlineStr"/>
+      <c r="H21" s="17" t="inlineStr"/>
+      <c r="I21" s="18" t="inlineStr"/>
     </row>
     <row r="22" ht="24" customHeight="1">
       <c r="A22" s="4" t="n">
@@ -1323,9 +1401,10 @@
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="9" t="inlineStr"/>
-      <c r="G22" s="10" t="inlineStr"/>
-      <c r="H22" s="11" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr"/>
+      <c r="H22" s="10" t="inlineStr"/>
+      <c r="I22" s="11" t="inlineStr"/>
     </row>
     <row r="23" ht="24" customHeight="1">
       <c r="A23" s="12" t="n">
@@ -1343,9 +1422,10 @@
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr"/>
-      <c r="F23" s="16" t="inlineStr"/>
-      <c r="G23" s="17" t="inlineStr"/>
-      <c r="H23" s="18" t="inlineStr"/>
+      <c r="F23" s="15" t="inlineStr"/>
+      <c r="G23" s="16" t="inlineStr"/>
+      <c r="H23" s="17" t="inlineStr"/>
+      <c r="I23" s="18" t="inlineStr"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="4" t="n">
@@ -1363,9 +1443,10 @@
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="9" t="inlineStr"/>
-      <c r="G24" s="10" t="inlineStr"/>
-      <c r="H24" s="11" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr"/>
+      <c r="H24" s="10" t="inlineStr"/>
+      <c r="I24" s="11" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="29" t="inlineStr">
@@ -1390,7 +1471,8 @@
       <c r="E27" s="31" t="n"/>
       <c r="F27" s="31" t="n"/>
       <c r="G27" s="31" t="n"/>
-      <c r="H27" s="32" t="n"/>
+      <c r="H27" s="31" t="n"/>
+      <c r="I27" s="32" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
       <c r="A28" s="33" t="inlineStr">
@@ -1408,7 +1490,8 @@
       <c r="E28" s="31" t="n"/>
       <c r="F28" s="31" t="n"/>
       <c r="G28" s="31" t="n"/>
-      <c r="H28" s="32" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="32" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="33" t="inlineStr">
@@ -1426,7 +1509,8 @@
       <c r="E29" s="31" t="n"/>
       <c r="F29" s="31" t="n"/>
       <c r="G29" s="31" t="n"/>
-      <c r="H29" s="32" t="n"/>
+      <c r="H29" s="31" t="n"/>
+      <c r="I29" s="32" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="33" t="inlineStr">
@@ -1444,7 +1528,8 @@
       <c r="E30" s="31" t="n"/>
       <c r="F30" s="31" t="n"/>
       <c r="G30" s="31" t="n"/>
-      <c r="H30" s="32" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="32" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="33" t="inlineStr">
@@ -1462,7 +1547,8 @@
       <c r="E31" s="31" t="n"/>
       <c r="F31" s="31" t="n"/>
       <c r="G31" s="31" t="n"/>
-      <c r="H31" s="32" t="n"/>
+      <c r="H31" s="31" t="n"/>
+      <c r="I31" s="32" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="33" t="inlineStr">
@@ -1480,7 +1566,8 @@
       <c r="E32" s="31" t="n"/>
       <c r="F32" s="31" t="n"/>
       <c r="G32" s="31" t="n"/>
-      <c r="H32" s="32" t="n"/>
+      <c r="H32" s="31" t="n"/>
+      <c r="I32" s="32" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="33" t="inlineStr">
@@ -1498,7 +1585,8 @@
       <c r="E33" s="31" t="n"/>
       <c r="F33" s="31" t="n"/>
       <c r="G33" s="31" t="n"/>
-      <c r="H33" s="32" t="n"/>
+      <c r="H33" s="31" t="n"/>
+      <c r="I33" s="32" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="33" t="inlineStr">
@@ -1516,7 +1604,8 @@
       <c r="E34" s="31" t="n"/>
       <c r="F34" s="31" t="n"/>
       <c r="G34" s="31" t="n"/>
-      <c r="H34" s="32" t="n"/>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="32" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="33" t="inlineStr">
@@ -1534,7 +1623,8 @@
       <c r="E35" s="31" t="n"/>
       <c r="F35" s="31" t="n"/>
       <c r="G35" s="31" t="n"/>
-      <c r="H35" s="32" t="n"/>
+      <c r="H35" s="31" t="n"/>
+      <c r="I35" s="32" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="33" t="inlineStr">
@@ -1552,7 +1642,8 @@
       <c r="E36" s="31" t="n"/>
       <c r="F36" s="31" t="n"/>
       <c r="G36" s="31" t="n"/>
-      <c r="H36" s="32" t="n"/>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="32" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
@@ -1570,7 +1661,8 @@
       <c r="E37" s="31" t="n"/>
       <c r="F37" s="31" t="n"/>
       <c r="G37" s="31" t="n"/>
-      <c r="H37" s="32" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="32" t="n"/>
     </row>
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="33" t="inlineStr">
@@ -1588,7 +1680,8 @@
       <c r="E38" s="31" t="n"/>
       <c r="F38" s="31" t="n"/>
       <c r="G38" s="31" t="n"/>
-      <c r="H38" s="32" t="n"/>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="32" t="n"/>
     </row>
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="33" t="inlineStr">
@@ -1606,7 +1699,8 @@
       <c r="E39" s="31" t="n"/>
       <c r="F39" s="31" t="n"/>
       <c r="G39" s="31" t="n"/>
-      <c r="H39" s="32" t="n"/>
+      <c r="H39" s="31" t="n"/>
+      <c r="I39" s="32" t="n"/>
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="33" t="inlineStr">
@@ -1624,7 +1718,8 @@
       <c r="E40" s="31" t="n"/>
       <c r="F40" s="31" t="n"/>
       <c r="G40" s="31" t="n"/>
-      <c r="H40" s="32" t="n"/>
+      <c r="H40" s="31" t="n"/>
+      <c r="I40" s="32" t="n"/>
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="33" t="inlineStr">
@@ -1642,7 +1737,8 @@
       <c r="E41" s="31" t="n"/>
       <c r="F41" s="31" t="n"/>
       <c r="G41" s="31" t="n"/>
-      <c r="H41" s="32" t="n"/>
+      <c r="H41" s="31" t="n"/>
+      <c r="I41" s="32" t="n"/>
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="34" t="inlineStr">
@@ -1654,200 +1750,208 @@
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="34" t="inlineStr">
         <is>
-          <t>※ [공통] 수정 대상은 소스코드를 추가 작성·수정해야 하는 파일이다. Interface 파일(RequestContextResolver.java 등)은 선언부만 보유하므로 수정 대상이 아니며, 해당 Interface 를 implements 한 구현체 클래스 파일을 기재한다. 경로는 src/main/java/com/koreanre/ifrs17/businessservice 하위이다.</t>
+          <t>※ [공통] 참조 데이터는 해당 단계가 판정에 사용하는 데이터의 출처이다. [Header] 표준 Header, [Body] 표준 Request Body, [Table] business_service Schema 테이블, [API] 외부 연동을 뜻한다.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="34" t="inlineStr">
         <is>
-          <t>※ [공통] 참조 데이터의 테이블·컬럼·유효값은 별도 [테이블 설계서] (business_service Schema, PostgreSQL) 를 기준으로 한다.</t>
+          <t>※ [공통] 수정 대상은 소스코드를 추가 작성·수정해야 하는 파일이다. Interface 파일(RequestContextResolver.java 등)은 선언부만 보유하므로 수정 대상이 아니며, 해당 Interface 를 implements 한 구현체 클래스 파일을 기재한다. 경로는 src/main/java/com/koreanre/ifrs17/businessservice 하위이다.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>※ [공통] 오류코드명은 동일 오류코드 안에서 실패 원인을 구분하기 위한 표기이며, 외부 응답의 message 문구는 구현 시 확정한다.</t>
+          <t>※ [공통] 참조 데이터의 테이블·컬럼·유효값은 별도 [테이블 설계서] (business_service Schema, PostgreSQL) 를 기준으로 한다.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="34" t="inlineStr">
         <is>
-          <t>※ [공통] 담당 컴포넌트는 Interface 기준 표기이다. 선언부는 Interface 에, 실제 로직은 구현체 클래스에 작성한다. 현행 구현체 : RequestContextResolver→HttpHeaderRequestContextResolver, ClientAuthenticationService→DummyClientAuthenticationService, ServiceMetadataRepository→InMemoryServiceMetadataRepository, AuthorizationService→DummyAuthorizationService. Dummy·InMemory 구현체는 DB 연동 시 교체 대상이다.</t>
+          <t>※ [공통] 오류코드명은 동일 오류코드 안에서 실패 원인을 구분하기 위한 표기이며, 외부 응답의 message 문구는 구현 시 확정한다.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 호출 Client 검증 단계에서는 BS_CLIENT 테이블만 조회하며, BS_CLIENT_SERVICE 테이블에는 접근하지 않는다.</t>
+          <t>※ [공통] 담당 컴포넌트는 Interface 기준 표기이다. 선언부는 Interface 에, 실제 로직은 구현체 클래스에 작성한다. 현행 구현체 : RequestContextResolver→HttpHeaderRequestContextResolver, ClientAuthenticationService→DummyClientAuthenticationService, ServiceMetadataRepository→InMemoryServiceMetadataRepository, AuthorizationService→DummyAuthorizationService. Dummy·InMemory 구현체는 DB 연동 시 교체 대상이다.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 세부 단계 (2) 는 BS_CLIENT 등록 여부와 active_yn = 'Y' 를 하나의 단계에서 판정하며, 두 경우 모두 부록 A 의 BS-AUTH-001(401) 로 처리한다. 미등록과 비활성은 응답 오류코드로 구분되지 않으며, 오류코드명과 감사 로그로 식별한다.</t>
+          <t>※ [3단계] 호출 Client 검증 단계에서는 BS_CLIENT 테이블만 조회하며, BS_CLIENT_SERVICE 테이블에는 접근하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+          <t>※ [3단계] 세부 단계 (2) 는 BS_CLIENT 등록 여부와 active_yn = 'Y' 를 하나의 단계에서 판정하며, 두 경우 모두 부록 A 의 BS-AUTH-001(401) 로 처리한다. 미등록과 비활성은 응답 오류코드로 구분되지 않으며, 오류코드명과 감사 로그로 식별한다.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="34" t="inlineStr">
         <is>
-          <t>※ [5단계] 세부 단계 (2) 는 BS_SERVICE.active_yn = 'Y', (4) 는 BS_SERVICE_VERSION.status_code = 'ACTIVE' 를 판정한다. 두 테이블의 상태 컬럼명이 서로 다른 점에 유의한다.</t>
+          <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 세부 단계 (2) 는 BS_SERVICE_ROLE 에 active_yn 컬럼이 없으므로 상태값을 판정하지 않는다. 테이블 설계서의 BS_SERVICE_ROLE 정의에 따라 필요 권한 코드(화면ID:액션) 존재 여부와 외부 권한 API 의 사용자 화면권한(Y/N) 을 AND 비교하여 판정한다.</t>
+          <t>※ [5단계] 세부 단계 (2) 는 BS_SERVICE.active_yn = 'Y', (4) 는 BS_SERVICE_VERSION.status_code = 'ACTIVE' 를 판정한다. 두 테이블의 상태 컬럼명이 서로 다른 점에 유의한다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] role_code 의 액션은 inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력) 5종이나, Phase 1 의 REST API 는 조회만 수행하므로 inqy 로 고정된다. 따라서 사용자 권한과 서비스 권한의 다대다 대조는 발생하지 않는다.</t>
+          <t>※ [6단계] 세부 단계 (2) 는 BS_SERVICE_ROLE 에 active_yn 컬럼이 없으므로 상태값을 판정하지 않는다. 테이블 설계서의 BS_SERVICE_ROLE 정의에 따라 필요 권한 코드(화면ID:액션) 존재 여부와 외부 권한 API 의 사용자 화면권한(Y/N) 을 AND 비교하여 판정한다.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 사용자 화면권한은 기존 IFRS17 권한 테이블을 Join 하여 취득하는 값이므로 Request 입력 항목이 아니다.</t>
+          <t>※ [6단계] role_code 의 액션은 inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력) 5종이나, Phase 1 의 REST API 는 조회만 수행하므로 inqy 로 고정된다. 따라서 사용자 권한과 서비스 권한의 다대다 대조는 발생하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 담당 컴포넌트 AuthorizationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 authorizeService 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+          <t>※ [6단계] 사용자 화면권한은 기존 IFRS17 권한 테이블을 Join 하여 취득하는 값이므로 Request 입력 항목이 아니다.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 파라미터의 데이터 타입·형식 검증은 별도 세부 단계로 두지 않는다. 타입 불일치는 (2) DTO 바인딩 시 변환 실패로 걸러지므로 추가 코드가 필요하지 않다.</t>
+          <t>※ [6단계] 담당 컴포넌트 AuthorizationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 authorizeService 단계를 담당할 컴포넌트로 명명한 것이다.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 허용값·허용범위 검증은 이번 구현 범위에서 제외한다. 서비스별 업무 규칙 성격이 강해 공통 단계에서 테이블 기반으로 일반화하면 코드량이 커지며, 설계서 10.2 예시와 같이 BusinessServiceHandler.validate() 에서 서비스별로 처리한다. 이에 따라 부록 A 의 BS-VAL-002(허용범위 초과)는 이번 구현 범위에서 발생 지점이 없다.</t>
+          <t>※ [7단계] 파라미터의 데이터 타입·형식 검증은 별도 세부 단계로 두지 않는다. 타입 불일치는 (2) DTO 바인딩 시 변환 실패로 걸러지므로 추가 코드가 필요하지 않다.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 검증 기준 데이터는 BS_SERVICE_PARAM 을 사용한다. BS_SERVICE_VERSION.request_schema 는 5단계 Service Catalog 활성 버전 조회의 대상 테이블 컬럼이므로 7단계 판정에는 사용하지 않는다.</t>
+          <t>※ [7단계] 허용값·허용범위 검증은 이번 구현 범위에서 제외한다. 서비스별 업무 규칙 성격이 강해 공통 단계에서 테이블 기반으로 일반화하면 코드량이 커지며, 설계서 10.2 예시와 같이 BusinessServiceHandler.validate() 에서 서비스별로 처리한다. 이에 따라 부록 A 의 BS-VAL-002(허용범위 초과)는 이번 구현 범위에서 발생 지점이 없다.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 업무 파라미터 기반 추가 권한 확인(6.1 인증과 권한 흐름 5항)은 이번 구현 범위에서 제외한다. 사용자 권한 판정은 4단계 사용자 Context 와 6단계 서비스/역할 권한 확인에서 종결되며, Phase 1 조회 서비스의 파라미터(기준년월·회계기준·보고서유형 등)에는 사용자별 접근 범위를 가르는 식별자가 없다. 설계서 10.2 예시도 해당 확인을 "필요 시" 조건부로 기술한다.</t>
+          <t>※ [7단계] 검증 기준 데이터는 BS_SERVICE_PARAM 을 사용한다. BS_SERVICE_VERSION.request_schema 는 5단계 Service Catalog 활성 버전 조회의 대상 테이블 컬럼이므로 7단계 판정에는 사용하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] BS_SERVICE_PARAM 은 테이블 설계서 시트를 확인하지 못했다. 필수 여부 컬럼명은 시트 확인 후 확정한다.</t>
+          <t>※ [7단계] 업무 파라미터 기반 추가 권한 확인(6.1 인증과 권한 흐름 5항)은 이번 구현 범위에서 제외한다. 사용자 권한 판정은 4단계 사용자 Context 와 6단계 서비스/역할 권한 확인에서 종결되며, Phase 1 조회 서비스의 파라미터(기준년월·회계기준·보고서유형 등)에는 사용자별 접근 범위를 가르는 식별자가 없다. 설계서 10.2 예시도 해당 확인을 "필요 시" 조건부로 기술한다.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="34" t="inlineStr">
         <is>
-          <t>※ 각 단계의 DB 접속 실패 등 인프라 오류는 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
+          <t>※ [7단계] BS_SERVICE_PARAM 은 테이블 설계서 시트를 확인하지 못했다. 필수 여부 컬럼명은 시트 확인 후 확정한다.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="34" t="inlineStr">
         <is>
-          <t>※ 예외 처리 절차(예외 클래스·실패 감사 로그·표준 Error Response 조립)는 기능 관점의 본 표와 성격이 달라 제외하였으며, 구현 착수 시점에 별도 표로 작성한다.</t>
+          <t>※ 각 단계의 DB 접속 실패 등 인프라 오류는 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="34" t="inlineStr">
         <is>
-          <t>※ [12단계 상세화 시 반영] 최종 허용/거부 결과의 감사 기록(authorization_result) 을 포함한다. 근거 : 6.1 인증과 권한 흐름 6항 / 6.3 감사로그 필수항목 — 보안 | remote_ip, auth_type, authorization_result.</t>
+          <t>※ 예외 처리 절차(예외 클래스·실패 감사 로그·표준 Error Response 조립)는 기능 관점의 본 표와 성격이 달라 제외하였으며, 구현 착수 시점에 별도 표로 작성한다.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="34" t="inlineStr">
         <is>
+          <t>※ [12단계 상세화 시 반영] 최종 허용/거부 결과의 감사 기록(authorization_result) 을 포함한다. 근거 : 6.1 인증과 권한 흐름 6항 / 6.3 감사로그 필수항목 — 보안 | remote_ip, auth_type, authorization_result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="34" t="inlineStr">
+        <is>
           <t>※ 1~2 · 8~13 단계의 세부 단계·현황·담당 컴포넌트·수정 대상·오류코드·오류코드명은 후속 상세화 시 기입한다. 4단계는 이번 구현 미대상이다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="48">
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="B40:H40"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A51:H51"/>
-    <mergeCell ref="A64:H64"/>
+  <mergeCells count="49">
+    <mergeCell ref="A65:I65"/>
+    <mergeCell ref="A46:I46"/>
     <mergeCell ref="B17:B18"/>
-    <mergeCell ref="A60:H60"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="A56:I56"/>
     <mergeCell ref="A11:A14"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="B33:H33"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B11:B14"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="B37:H37"/>
-    <mergeCell ref="A61:H61"/>
-    <mergeCell ref="B36:H36"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="B41:H41"/>
-    <mergeCell ref="B35:H35"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="B31:H31"/>
+    <mergeCell ref="B27:I27"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A57:I57"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="B39:I39"/>
+    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A53:I53"/>
+    <mergeCell ref="A62:I62"/>
     <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="A43:I43"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A55:H55"/>
-    <mergeCell ref="B27:H27"/>
+    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="A63:I63"/>
+    <mergeCell ref="B29:I29"/>
     <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A57:H57"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="B39:H39"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A62:H62"/>
-    <mergeCell ref="A53:H53"/>
-    <mergeCell ref="A43:H43"/>
-    <mergeCell ref="A63:H63"/>
-    <mergeCell ref="A52:H52"/>
+    <mergeCell ref="B38:I38"/>
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="A44:I44"/>
+    <mergeCell ref="B28:I28"/>
+    <mergeCell ref="B37:I37"/>
+    <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A48:I48"/>
+    <mergeCell ref="B40:I40"/>
+    <mergeCell ref="A64:I64"/>
+    <mergeCell ref="A59:I59"/>
+    <mergeCell ref="B30:I30"/>
+    <mergeCell ref="A49:I49"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="B33:I33"/>
+    <mergeCell ref="A60:I60"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B38:H38"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="A44:H44"/>
-    <mergeCell ref="B34:H34"/>
-    <mergeCell ref="A58:H58"/>
-    <mergeCell ref="B28:H28"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="B36:I36"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="B41:I41"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -1242,7 +1242,7 @@
       <c r="C17" s="21" t="inlineStr">
         <is>
           <t>(1) 테이블 BS_SERVICE_PARAM 의 PK 인 (service_id, version, param_name) 로 요청 serviceId 와 확정 version 의
-파라미터 정의 목록을 조회하고, 필수 파라미터가 Request 의 parameters 에 모두 입력되었는지 체크한다.
+파라미터 정의 목록을 조회하고, required_yn 이 'Y' 인 필수 파라미터가 Request 의 parameters 에 모두 입력되었는지 체크한다.
 → 모두 입력되어 있으면 (2) 단계 진행</t>
         </is>
       </c>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>7.2 주요 테이블 — BS_SERVICE_PARAM | 입력 파라미터 정의 | service_id, version, param_name (테이블 설계서 시트 미확인)</t>
+          <t>테이블 설계서 BS_SERVICE_PARAM (business_service.bs_service_param, 논리명 입력 파라미터 정의, PK service_id + version + param_name) — required_yn char(1) NOT NULL DEFAULT 'Y', Y(필수)/N(선택), "필수 여부"   ·   param_type varchar(30) NOT NULL, STRING/NUMBER/BOOLEAN/DATE 등, "파라미터 데이터 타입"   ·   param_description varchar(300), "파라미터 설명"   ·   display_order integer NOT NULL DEFAULT 1, "화면 표시 순서"   /   service_id 는 FK→BS_SERVICE_VERSION, version 은 FK   /   출처 : 상세설계서 v1.3 §7.2 (신규)</t>
         </is>
       </c>
       <c r="C40" s="31" t="n"/>
@@ -1841,7 +1841,7 @@
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 파라미터의 데이터 타입·형식 검증은 별도 세부 단계로 두지 않는다. 타입 불일치는 (2) DTO 바인딩 시 변환 실패로 걸러지므로 추가 코드가 필요하지 않다.</t>
+          <t>※ [7단계] 파라미터의 데이터 타입·형식 검증은 별도 세부 단계로 두지 않는다. BS_SERVICE_PARAM 에 param_type (STRING/NUMBER/BOOLEAN/DATE 등) 이 정의되어 있으나, 타입 불일치는 (2) DTO 바인딩 시 변환 실패로 걸러지므로 추가 코드가 필요하지 않다.</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] BS_SERVICE_PARAM 은 테이블 설계서 시트를 확인하지 못했다. 필수 여부 컬럼명은 시트 확인 후 확정한다.</t>
+          <t>※ [7단계] 필수 파라미터 판정 컬럼은 BS_SERVICE_PARAM.required_yn (char(1), DEFAULT 'Y', Y(필수)/N(선택)) 이며, 테이블 설계서 확인으로 확정하였다. param_description 은 설명 항목, display_order 는 화면 표시 순서 항목이므로 7단계 판정에는 사용하지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1913,8 +1913,8 @@
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B11:B14"/>
     <mergeCell ref="B27:I27"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B39:I39"/>

--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -145,7 +145,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -244,11 +244,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -338,6 +358,8 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -703,7 +725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -822,369 +844,425 @@
           <t>Request ID 생성 또는 검증</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr"/>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>(1) 필수 Header 의 X-Request-ID 가 입력되었는지 체크한다.
+→ 미입력이면 서버(BSL WAS)가 BS_CALL_LOG 의 PK 양식(REQ-yyyyMMdd-0000)으로 채번하여 request_id 를 확정하고 다음 프로세스 진행
+→ 입력되어 있으면 (2) 단계 진행</t>
+        </is>
+      </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr"/>
+      <c r="E7" s="15" t="inlineStr">
+        <is>
+          <t>RequestContextResolver
+resolve(HttpServletRequest,
+           serviceId, request)
+IdGenerator.newRequestId()</t>
+        </is>
+      </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>[Header] X-Request-ID, X-Trace-ID</t>
-        </is>
-      </c>
-      <c r="G7" s="16" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-      <c r="I7" s="18" t="inlineStr"/>
+          <t>[Header] X-Request-ID</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>HttpHeaderRequestContextResolver.java
+IdGenerator.java</t>
+        </is>
+      </c>
+      <c r="H7" s="17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>호출 Client 검증</t>
-        </is>
-      </c>
+      <c r="A8" s="26" t="n"/>
+      <c r="B8" s="26" t="n"/>
       <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>(2) 입력된 X-Request-ID 원본을 BS_CALL_LOG 의 client_request_id 컬럼 적재값으로 확정하고,
+PK 인 request_id 는 서버가 PK 양식(REQ-yyyyMMdd-0000)으로 재채번한다.
+→ request_id 와 client_request_id 가 모두 확정되면 다음 프로세스 진행</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>예정</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>RequestContextResolver
+resolve(HttpServletRequest,
+           serviceId, request)
+IdGenerator.newRequestId()</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>[Header] X-Request-ID
+[Table] BS_CALL_LOG</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
+        <is>
+          <t>HttpHeaderRequestContextResolver.java
+IdGenerator.java
+ServiceContext.java
+BsCallLog.java</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I8" s="25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="50" customHeight="1">
+      <c r="A9" s="35" t="n"/>
+      <c r="B9" s="35" t="n"/>
+      <c r="C9" s="21" t="inlineStr">
         <is>
           <t>(1) 필수 Header 의 X-Client-ID 가 아예 입력되지 않았는지 필수입력값 유효성을 체크한다.
 → 입력되어 있으면 (2) 단계 진행</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>RequestContextResolver
 resolve(HttpServletRequest,
           serviceId, request)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>[Header] X-Client-ID</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>HttpHeaderRequestContextResolver.java</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>BS-VAL-001
 HTTP 400</t>
         </is>
       </c>
-      <c r="I8" s="25" t="inlineStr">
+      <c r="I9" s="25" t="inlineStr">
         <is>
           <t>Client ID 미입력</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="26" t="n"/>
-      <c r="B9" s="26" t="n"/>
-      <c r="C9" s="21" t="inlineStr">
+    <row r="10" ht="50" customHeight="1">
+      <c r="A10" s="35" t="n"/>
+      <c r="B10" s="35" t="n"/>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>(2) BS_CLIENT 테이블의 PK 인 client_id 값이 X-Client-ID 와 같은 데이터가 있는지 체크하고,
 있으면 해당 데이터의 active_yn 컬럼값이 'Y' 인지 체크한다.
 → 'Y' 이면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>ClientAuthenticationService
 authenticate(ServiceContext)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_CLIENT</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>DummyClientAuthenticationService.java</t>
         </is>
       </c>
-      <c r="H9" s="24" t="inlineStr">
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-001
 HTTP 401</t>
         </is>
       </c>
-      <c r="I9" s="25" t="inlineStr">
+      <c r="I10" s="25" t="inlineStr">
         <is>
           <t>미등록 Client
 미사용 Client</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="12" t="n">
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>SSO 사용자 Context 추출</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="27" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="27" t="inlineStr">
         <is>
           <t>미대상</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr"/>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr"/>
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t>[Header] Authorization, X-User-ID</t>
         </is>
       </c>
-      <c r="G10" s="16" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-      <c r="I10" s="18" t="inlineStr"/>
-    </row>
-    <row r="11" ht="50" customHeight="1">
-      <c r="A11" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>Service Catalog에서 활성 버전 조회</t>
-        </is>
-      </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="G11" s="16" t="inlineStr"/>
+      <c r="H11" s="17" t="inlineStr"/>
+      <c r="I11" s="18" t="inlineStr"/>
+    </row>
+    <row r="12" ht="50" customHeight="1">
+      <c r="A12" s="35" t="n"/>
+      <c r="B12" s="35" t="n"/>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>(1) service ID 가 존재하는지
 → 존재하면 (2)</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_SERVICE</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="H11" s="24" t="inlineStr">
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="I11" s="25" t="inlineStr">
+      <c r="I12" s="25" t="inlineStr">
         <is>
           <t>서비스 미존재</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="28" t="n"/>
-      <c r="C12" s="21" t="inlineStr">
+    <row r="13" ht="50" customHeight="1">
+      <c r="A13" s="36" t="n"/>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>(2) 해당 service ID의 사용여부가 "사용" 상태인지
 → 사용상태면 (3)</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_SERVICE</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="H12" s="24" t="inlineStr">
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="I12" s="25" t="inlineStr">
+      <c r="I13" s="25" t="inlineStr">
         <is>
           <t>서비스 미사용</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="50" customHeight="1">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="21" t="inlineStr">
+    <row r="14" ht="50" customHeight="1">
+      <c r="A14" s="36" t="n"/>
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>(3) 버전 정보가 존재하는지
 → 존재하면 (4)</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_SERVICE_VERSION</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="H13" s="24" t="inlineStr">
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="I13" s="25" t="inlineStr">
+      <c r="I14" s="25" t="inlineStr">
         <is>
           <t>버전 미존재</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="50" customHeight="1">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="26" t="n"/>
-      <c r="C14" s="21" t="inlineStr">
+    <row r="15" ht="50" customHeight="1">
+      <c r="A15" s="35" t="n"/>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>(4) 조회된 버전 정보의 상태가 "사용" 상태인지
 → 사용상태면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>ServiceMetadataRepository
 findActive(serviceId, version)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_SERVICE_VERSION</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>InMemoryServiceMetadataRepository.java</t>
         </is>
       </c>
-      <c r="H14" s="24" t="inlineStr">
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>BS-SVC-404
 HTTP 404</t>
         </is>
       </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="I15" s="25" t="inlineStr">
         <is>
           <t>버전 미사용(INACTIVE)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="50" customHeight="1">
-      <c r="A15" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>서비스/역할 권한 확인</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+    <row r="16" ht="50" customHeight="1">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>(1) 테이블 BS_CLIENT_SERVICE 의 PK 인 (client_id, service_id) 가 (X-Client-ID Header 값, 요청 serviceId) 와
 같은 데이터가 있는지 체크하고, 있으면 해당 데이터의 active_yn 컬럼값이 'Y' 인지 체크한다.
 → 'Y' 이면 (2) 단계 진행</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>AuthorizationService
 authorize(ServiceContext,
             ServiceMetadata)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_CLIENT_SERVICE</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>DummyAuthorizationService.java</t>
         </is>
       </c>
-      <c r="H15" s="24" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-003
 HTTP 403</t>
         </is>
       </c>
-      <c r="I15" s="25" t="inlineStr">
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Client 호출 허용 미등록
 Client 호출 차단</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="26" t="n"/>
-      <c r="B16" s="26" t="n"/>
-      <c r="C16" s="21" t="inlineStr">
+    <row r="17" ht="50" customHeight="1">
+      <c r="A17" s="35" t="n"/>
+      <c r="B17" s="35" t="n"/>
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>(2) 테이블 BS_SERVICE_ROLE 의 PK 인 (service_id, role_code) 에서 요청 serviceId 의 필요 권한 코드
 (화면ID:액션) 를 조회하고, 기존 IFRS17 권한정보(외부 권한 API)의 사용자 화면권한(Y/N) 과
@@ -1192,12 +1270,12 @@
 → 모두 'Y' 이면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>AuthorizationService
 authorize(ServiceContext,
@@ -1205,284 +1283,259 @@
 + 기존 IFRS17 권한 API</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_SERVICE_ROLE
 [API] 기존 IFRS17 권한 API</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>DummyAuthorizationService.java
 (신규) 권한 API 연동 Adapter</t>
         </is>
       </c>
-      <c r="H16" s="24" t="inlineStr">
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>BS-AUTH-003
 HTTP 403</t>
         </is>
       </c>
-      <c r="I16" s="25" t="inlineStr">
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>서비스 필요권한 미정의
 사용자 화면권한 없음</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="50" customHeight="1">
-      <c r="A17" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>입력 Schema 및 업무 파라미터 검증</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
+    <row r="18" ht="50" customHeight="1">
+      <c r="A18" s="35" t="n"/>
+      <c r="B18" s="35" t="n"/>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>(1) 테이블 BS_SERVICE_PARAM 의 PK 인 (service_id, version, param_name) 로 요청 serviceId 와 확정 version 의
 파라미터 정의 목록을 조회하고, required_yn 이 'Y' 인 필수 파라미터가 Request 의 parameters 에 모두 입력되었는지 체크한다.
 → 모두 입력되어 있으면 (2) 단계 진행</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>StandardRequestValidator
 validate(StandardRequest,
            ServiceMetadata)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>[Table] BS_SERVICE_PARAM</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>StandardRequestValidator.java</t>
         </is>
       </c>
-      <c r="H17" s="24" t="inlineStr">
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>BS-VAL-001
 HTTP 400</t>
         </is>
       </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="I18" s="25" t="inlineStr">
         <is>
           <t>필수 파라미터 미입력</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="26" t="n"/>
-      <c r="B18" s="26" t="n"/>
-      <c r="C18" s="21" t="inlineStr">
+    <row r="19" ht="50" customHeight="1">
+      <c r="A19" s="35" t="n"/>
+      <c r="B19" s="35" t="n"/>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>(2) 검증을 통과한 parameters 를 서비스별 요청 DTO 로 바인딩한다.
 → 바인딩에 성공하면 다음 프로세스 진행</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>ParameterBinder
 bind(parameters, requestType)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>ParameterBinder.java</t>
         </is>
       </c>
-      <c r="H18" s="24" t="inlineStr">
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>BS-VAL-001
 HTTP 400</t>
         </is>
       </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>DTO 바인딩 실패</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="12" t="n">
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>감사 시작 로그 기록</t>
         </is>
       </c>
-      <c r="C19" s="14" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="C20" s="14" t="inlineStr"/>
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr"/>
-      <c r="F19" s="15" t="inlineStr"/>
-      <c r="G19" s="16" t="inlineStr"/>
-      <c r="H19" s="17" t="inlineStr"/>
-      <c r="I19" s="18" t="inlineStr"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="4" t="n">
+      <c r="E20" s="15" t="inlineStr"/>
+      <c r="F20" s="15" t="inlineStr"/>
+      <c r="G20" s="16" t="inlineStr"/>
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="18" t="inlineStr"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Business Service Handler 실행</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr"/>
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="10" t="inlineStr"/>
-      <c r="I20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21" ht="24" customHeight="1">
-      <c r="A21" s="12" t="n">
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr"/>
+      <c r="H21" s="10" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="13" t="inlineStr">
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>Legacy Adapter를 통한 기존 Service 호출</t>
         </is>
       </c>
-      <c r="C21" s="14" t="inlineStr"/>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="C22" s="14" t="inlineStr"/>
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr"/>
-      <c r="F21" s="15" t="inlineStr"/>
-      <c r="G21" s="16" t="inlineStr"/>
-      <c r="H21" s="17" t="inlineStr"/>
-      <c r="I21" s="18" t="inlineStr"/>
-    </row>
-    <row r="22" ht="24" customHeight="1">
-      <c r="A22" s="4" t="n">
+      <c r="E22" s="15" t="inlineStr"/>
+      <c r="F22" s="15" t="inlineStr"/>
+      <c r="G22" s="16" t="inlineStr"/>
+      <c r="H22" s="17" t="inlineStr"/>
+      <c r="I22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>결과 DTO를 표준 JSON으로 변환 및 마스킹</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr"/>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="10" t="inlineStr"/>
-      <c r="I22" s="11" t="inlineStr"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="12" t="n">
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr"/>
+      <c r="H23" s="10" t="inlineStr"/>
+      <c r="I23" s="11" t="inlineStr"/>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>감사 성공/실패 로그 기록</t>
         </is>
       </c>
-      <c r="C23" s="14" t="inlineStr"/>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="C24" s="14" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr"/>
-      <c r="F23" s="15" t="inlineStr"/>
-      <c r="G23" s="16" t="inlineStr"/>
-      <c r="H23" s="17" t="inlineStr"/>
-      <c r="I23" s="18" t="inlineStr"/>
-    </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="n">
+      <c r="E24" s="15" t="inlineStr"/>
+      <c r="F24" s="15" t="inlineStr"/>
+      <c r="G24" s="16" t="inlineStr"/>
+      <c r="H24" s="17" t="inlineStr"/>
+      <c r="I24" s="18" t="inlineStr"/>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>표준 Response 반환</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr"/>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr"/>
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>예정</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="10" t="inlineStr"/>
-      <c r="I24" s="11" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
+      <c r="H25" s="10" t="inlineStr"/>
+      <c r="I25" s="11" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>기입 근거</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B27" s="30" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>설계서 근거</t>
-        </is>
-      </c>
-      <c r="C27" s="31" t="n"/>
-      <c r="D27" s="31" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="31" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="32" t="n"/>
-    </row>
-    <row r="28" ht="26" customHeight="1">
-      <c r="A28" s="33" t="inlineStr">
-        <is>
-          <t>3단계 · 담당 컴포넌트</t>
-        </is>
-      </c>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>4.2 핵심 컴포넌트 — RequestContextResolver | SSO/Client/Request ID/Trace 정보 생성   /   10.4 공통 Executor 의사코드 — resolveContext → validateClient</t>
         </is>
       </c>
       <c r="C28" s="31" t="n"/>
@@ -1496,12 +1549,12 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="33" t="inlineStr">
         <is>
-          <t>3단계 · 오류코드</t>
+          <t>2단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   ·   BS-AUTH-001 | 401 | 인증 실패   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001   ·   인증 실패 | 401 | BS-AUTH-001 | SSO/Client 인증 실패   /   5.2 필수 Header — X-Client-ID | Y | 호출 채널 식별</t>
+          <t>4.2 핵심 컴포넌트 — RequestContextResolver | SSO/Client/Request ID/Trace 정보 생성   /   10.4 공통 Executor 의사코드 — resolveContext   /   현행 코드 HttpHeaderRequestContextResolver.resolve(HttpServletRequest, String, StandardRequest) · IdGenerator.newRequestId()</t>
         </is>
       </c>
       <c r="C29" s="31" t="n"/>
@@ -1515,12 +1568,12 @@
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="33" t="inlineStr">
         <is>
-          <t>3단계 · 참조 데이터</t>
+          <t>2단계 · 생성 규칙</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_CLIENT (business_service.bs_client, PK client_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용), "N이면 인증 차단" [핵심 로직]</t>
+          <t>5.2 필수 Header — X-Request-ID | N(선택) | 미입력 시 서버 생성(REQ-yyyyMMdd-0001)   /   BSL-F-07 입력→출력 데이터 — requestId | 입력 출처 Header X-Request-ID | 미입력 시 생성 규칙 REQ-yyyyMMdd-0001 (AtomicInteger) | 저장 위치 ServiceContext.requestId   /   12.3 장애 대응 — requestId 를 추적 기준 키로 사용</t>
         </is>
       </c>
       <c r="C30" s="31" t="n"/>
@@ -1534,12 +1587,12 @@
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="33" t="inlineStr">
         <is>
-          <t>5단계 · 담당 컴포넌트</t>
+          <t>2단계 · 오류코드</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>4.2 핵심 컴포넌트 — ServiceMetadataRepository | 서비스 버전·상태·권한·Timeout 조회 | findActive(serviceId, version)</t>
+          <t>BSL-F-07 Request ID 생성 또는 검증 — 오류코드 : 없음. Header 입력 유무에 따른 분기만 수행하며 요청을 거부하는 판정이 없다.</t>
         </is>
       </c>
       <c r="C31" s="31" t="n"/>
@@ -1553,12 +1606,12 @@
     <row r="32" ht="26" customHeight="1">
       <c r="A32" s="33" t="inlineStr">
         <is>
-          <t>5단계 · 오류코드</t>
+          <t>2단계 · 참조 데이터</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-SVC-404 | 404 | 서비스/버전 없음 또는 비활성   /   4.5 예외 처리 기준 — 서비스 없음/비활성 | 404 | BS-SVC-404 | Catalog 상태 확인</t>
+          <t>테이블 설계서 BS_CALL_LOG (business_service.bs_call_log, PK request_id) — 6.3 감사로그 필수항목 · 7.3 핵심 DDL 의 호출 이력 저장 테이블   /   client_request_id 컬럼은 테이블 설계서 시트로 확인하지 못했다 (현행 스켈레톤 BsCallLog.java 에 미정의)</t>
         </is>
       </c>
       <c r="C32" s="31" t="n"/>
@@ -1572,12 +1625,12 @@
     <row r="33" ht="26" customHeight="1">
       <c r="A33" s="33" t="inlineStr">
         <is>
-          <t>5단계 · 참조 데이터</t>
+          <t>3단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_SERVICE (PK service_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용) [핵심 로직]   /   BS_SERVICE_VERSION (PK service_id + version) — status_code varchar(20) DEFAULT 'ACTIVE', ACTIVE(활성)/INACTIVE(비활성), "활성 버전만 실행" [핵심 로직]</t>
+          <t>4.2 핵심 컴포넌트 — RequestContextResolver | SSO/Client/Request ID/Trace 정보 생성   /   10.4 공통 Executor 의사코드 — resolveContext → validateClient</t>
         </is>
       </c>
       <c r="C33" s="31" t="n"/>
@@ -1591,12 +1644,12 @@
     <row r="34" ht="26" customHeight="1">
       <c r="A34" s="33" t="inlineStr">
         <is>
-          <t>5단계 (2) 즉시 차단</t>
+          <t>3단계 · 오류코드</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>8.4 서비스 등록 및 외부 공개 흐름 7항 — 사용 여부를 "미사용"으로 변경하면 즉시 신규 호출을 차단한다</t>
+          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   ·   BS-AUTH-001 | 401 | 인증 실패   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001   ·   인증 실패 | 401 | BS-AUTH-001 | SSO/Client 인증 실패   /   5.2 필수 Header — X-Client-ID | Y | 호출 채널 식별</t>
         </is>
       </c>
       <c r="C34" s="31" t="n"/>
@@ -1610,12 +1663,12 @@
     <row r="35" ht="26" customHeight="1">
       <c r="A35" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 담당 컴포넌트</t>
+          <t>3단계 · 참조 데이터</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
         <is>
-          <t>10.4 공통 Executor 의사코드 — authorizeService   /   4.4 표준 인터페이스 — BusinessServiceHandler.authorize(context, request) (업무 파라미터 단위 추가 권한)</t>
+          <t>테이블 설계서 BS_CLIENT (business_service.bs_client, PK client_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용), "N이면 인증 차단" [핵심 로직]</t>
         </is>
       </c>
       <c r="C35" s="31" t="n"/>
@@ -1629,12 +1682,12 @@
     <row r="36" ht="26" customHeight="1">
       <c r="A36" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 오류코드</t>
+          <t>5단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-AUTH-003 | 403 | 서비스 권한 없음   /   4.5 예외 처리 기준 — 권한 없음 | 403 | BS-AUTH-003 | 서비스 ID와 사용자 정보 감사   /   11.2 필수 인수 시나리오 — 권한 없음 | 유효 사용자, 역할 없음 | 403/BS-AUTH-003</t>
+          <t>4.2 핵심 컴포넌트 — ServiceMetadataRepository | 서비스 버전·상태·권한·Timeout 조회 | findActive(serviceId, version)</t>
         </is>
       </c>
       <c r="C36" s="31" t="n"/>
@@ -1648,12 +1701,12 @@
     <row r="37" ht="26" customHeight="1">
       <c r="A37" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 참조 데이터</t>
+          <t>5단계 · 오류코드</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_CLIENT_SERVICE (PK client_id + service_id) — active_yn char(1) DEFAULT 'Y', Y(허용)/N(차단), "호출 허용 여부" [핵심 로직]   /   BS_SERVICE_ROLE (PK service_id + role_code) — role_code varchar(100), 화면ID:액션 형식, 화면ID=[A-Z]{4}M[0-9]{3}, 액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력), 예) CLSGM001:inqy</t>
+          <t>부록 A 표준 오류코드 — BS-SVC-404 | 404 | 서비스/버전 없음 또는 비활성   /   4.5 예외 처리 기준 — 서비스 없음/비활성 | 404 | BS-SVC-404 | Catalog 상태 확인</t>
         </is>
       </c>
       <c r="C37" s="31" t="n"/>
@@ -1667,12 +1720,12 @@
     <row r="38" ht="26" customHeight="1">
       <c r="A38" s="33" t="inlineStr">
         <is>
-          <t>7단계 · 담당 컴포넌트</t>
+          <t>5단계 · 참조 데이터</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>4.3-12 입력 Schema 및 업무 파라미터 검증   /   10.4 공통 Executor 의사코드 — authorizeService 이후 invokeHandler 이전   /   현행 코드 StandardRequestValidator.validate(StandardRequest, ServiceMetadata) · ParameterBinder.bind(Map, Class)</t>
+          <t>테이블 설계서 BS_SERVICE (PK service_id) — active_yn char(1) DEFAULT 'Y', Y(사용)/N(미사용) [핵심 로직]   /   BS_SERVICE_VERSION (PK service_id + version) — status_code varchar(20) DEFAULT 'ACTIVE', ACTIVE(활성)/INACTIVE(비활성), "활성 버전만 실행" [핵심 로직]</t>
         </is>
       </c>
       <c r="C38" s="31" t="n"/>
@@ -1686,12 +1739,12 @@
     <row r="39" ht="26" customHeight="1">
       <c r="A39" s="33" t="inlineStr">
         <is>
-          <t>7단계 · 오류코드</t>
+          <t>5단계 (2) 즉시 차단</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001 | 필드별 오류 반환, Stack Trace 금지   /   11.2 필수 인수 시나리오 — 입력 오류 | 잘못된 YYYY-MM | 400/BS-VAL-001</t>
+          <t>8.4 서비스 등록 및 외부 공개 흐름 7항 — 사용 여부를 "미사용"으로 변경하면 즉시 신규 호출을 차단한다</t>
         </is>
       </c>
       <c r="C39" s="31" t="n"/>
@@ -1705,12 +1758,12 @@
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="33" t="inlineStr">
         <is>
-          <t>7단계 · 참조 데이터</t>
+          <t>6단계 · 담당 컴포넌트</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_SERVICE_PARAM (business_service.bs_service_param, 논리명 입력 파라미터 정의, PK service_id + version + param_name) — required_yn char(1) NOT NULL DEFAULT 'Y', Y(필수)/N(선택), "필수 여부"   ·   param_type varchar(30) NOT NULL, STRING/NUMBER/BOOLEAN/DATE 등, "파라미터 데이터 타입"   ·   param_description varchar(300), "파라미터 설명"   ·   display_order integer NOT NULL DEFAULT 1, "화면 표시 순서"   /   service_id 는 FK→BS_SERVICE_VERSION, version 은 FK   /   출처 : 상세설계서 v1.3 §7.2 (신규)</t>
+          <t>10.4 공통 Executor 의사코드 — authorizeService   /   4.4 표준 인터페이스 — BusinessServiceHandler.authorize(context, request) (업무 파라미터 단위 추가 권한)</t>
         </is>
       </c>
       <c r="C40" s="31" t="n"/>
@@ -1724,12 +1777,12 @@
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="33" t="inlineStr">
         <is>
-          <t>6단계 · 권한 원칙</t>
+          <t>6단계 · 오류코드</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>6.2 권한 원칙 — 서비스 권한은 BS_SERVICE_ROLE 과 기존 IFRS17 권한정보를 함께 사용한다   /   테이블 설계서 BS_SERVICE_ROLE 설명 — "외부 권한API의 사용자 화면권한(Y/N)과 AND 비교(§6.2 권한 원칙)"</t>
+          <t>부록 A 표준 오류코드 — BS-AUTH-003 | 403 | 서비스 권한 없음   /   4.5 예외 처리 기준 — 권한 없음 | 403 | BS-AUTH-003 | 서비스 ID와 사용자 정보 감사   /   11.2 필수 인수 시나리오 — 권한 없음 | 유효 사용자, 역할 없음 | 403/BS-AUTH-003</t>
         </is>
       </c>
       <c r="C41" s="31" t="n"/>
@@ -1740,217 +1793,335 @@
       <c r="H41" s="31" t="n"/>
       <c r="I41" s="32" t="n"/>
     </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="33" t="inlineStr">
+        <is>
+          <t>6단계 · 참조 데이터</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>테이블 설계서 BS_CLIENT_SERVICE (PK client_id + service_id) — active_yn char(1) DEFAULT 'Y', Y(허용)/N(차단), "호출 허용 여부" [핵심 로직]   /   BS_SERVICE_ROLE (PK service_id + role_code) — role_code varchar(100), 화면ID:액션 형식, 화면ID=[A-Z]{4}M[0-9]{3}, 액션=inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력), 예) CLSGM001:inqy</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="31" t="n"/>
+      <c r="E42" s="31" t="n"/>
+      <c r="F42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="31" t="n"/>
+      <c r="I42" s="32" t="n"/>
+    </row>
     <row r="43" ht="26" customHeight="1">
-      <c r="A43" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 현황은 이번 업무의뢰의 구현 대상 여부와 진행 상태를 표기한다. 예정 = 구현 진행 예정, 완료 = 구현 진행 완료, 미대상 = 이번 구현 범위가 아님. 4단계 SSO 사용자 Context 추출은 이번 구현 대상이 아니므로 미대상으로 표기한다.</t>
+      <c r="A43" s="33" t="inlineStr">
+        <is>
+          <t>7단계 · 담당 컴포넌트</t>
         </is>
       </c>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="A44" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 참조 데이터는 해당 단계가 판정에 사용하는 데이터의 출처이다. [Header] 표준 Header, [Body] 표준 Request Body, [Table] business_service Schema 테이블, [API] 외부 연동을 뜻한다.</t>
+      <c r="A44" s="33" t="inlineStr">
+        <is>
+          <t>7단계 · 오류코드</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 수정 대상은 소스코드를 추가 작성·수정해야 하는 파일이다. Interface 파일(RequestContextResolver.java 등)은 선언부만 보유하므로 수정 대상이 아니며, 해당 Interface 를 implements 한 구현체 클래스 파일을 기재한다. 경로는 src/main/java/com/koreanre/ifrs17/businessservice 하위이다.</t>
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>7단계 · 참조 데이터</t>
         </is>
       </c>
     </row>
     <row r="46" ht="26" customHeight="1">
-      <c r="A46" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 참조 데이터의 테이블·컬럼·유효값은 별도 [테이블 설계서] (business_service Schema, PostgreSQL) 를 기준으로 한다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="34" t="inlineStr">
-        <is>
-          <t>※ [공통] 오류코드명은 동일 오류코드 안에서 실패 원인을 구분하기 위한 표기이며, 외부 응답의 message 문구는 구현 시 확정한다.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A46" s="33" t="inlineStr">
+        <is>
+          <t>6단계 · 권한 원칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1"/>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="34" t="inlineStr">
         <is>
-          <t>※ [공통] 담당 컴포넌트는 Interface 기준 표기이다. 선언부는 Interface 에, 실제 로직은 구현체 클래스에 작성한다. 현행 구현체 : RequestContextResolver→HttpHeaderRequestContextResolver, ClientAuthenticationService→DummyClientAuthenticationService, ServiceMetadataRepository→InMemoryServiceMetadataRepository, AuthorizationService→DummyAuthorizationService. Dummy·InMemory 구현체는 DB 연동 시 교체 대상이다.</t>
+          <t>※ [공통] 현황은 이번 업무의뢰의 구현 대상 여부와 진행 상태를 표기한다. 예정 = 구현 진행 예정, 완료 = 구현 진행 완료, 미대상 = 이번 구현 범위가 아님. 4단계 SSO 사용자 Context 추출은 이번 구현 대상이 아니므로 미대상으로 표기한다.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 호출 Client 검증 단계에서는 BS_CLIENT 테이블만 조회하며, BS_CLIENT_SERVICE 테이블에는 접근하지 않는다.</t>
+          <t>※ [공통] 참조 데이터는 해당 단계가 판정에 사용하는 데이터의 출처이다. [Header] 표준 Header, [Body] 표준 Request Body, [Table] business_service Schema 테이블, [API] 외부 연동을 뜻한다.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 세부 단계 (2) 는 BS_CLIENT 등록 여부와 active_yn = 'Y' 를 하나의 단계에서 판정하며, 두 경우 모두 부록 A 의 BS-AUTH-001(401) 로 처리한다. 미등록과 비활성은 응답 오류코드로 구분되지 않으며, 오류코드명과 감사 로그로 식별한다.</t>
+          <t>※ [공통] 수정 대상은 소스코드를 추가 작성·수정해야 하는 파일이다. Interface 파일(RequestContextResolver.java 등)은 선언부만 보유하므로 수정 대상이 아니며, 해당 Interface 를 implements 한 구현체 클래스 파일을 기재한다. 경로는 src/main/java/com/koreanre/ifrs17/businessservice 하위이다.</t>
         </is>
       </c>
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="34" t="inlineStr">
         <is>
-          <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+          <t>※ [공통] 참조 데이터의 테이블·컬럼·유효값은 별도 [테이블 설계서] (business_service Schema, PostgreSQL) 를 기준으로 한다.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="34" t="inlineStr">
         <is>
-          <t>※ [5단계] 세부 단계 (2) 는 BS_SERVICE.active_yn = 'Y', (4) 는 BS_SERVICE_VERSION.status_code = 'ACTIVE' 를 판정한다. 두 테이블의 상태 컬럼명이 서로 다른 점에 유의한다.</t>
+          <t>※ [공통] 오류코드명은 동일 오류코드 안에서 실패 원인을 구분하기 위한 표기이며, 외부 응답의 message 문구는 구현 시 확정한다.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 세부 단계 (2) 는 BS_SERVICE_ROLE 에 active_yn 컬럼이 없으므로 상태값을 판정하지 않는다. 테이블 설계서의 BS_SERVICE_ROLE 정의에 따라 필요 권한 코드(화면ID:액션) 존재 여부와 외부 권한 API 의 사용자 화면권한(Y/N) 을 AND 비교하여 판정한다.</t>
+          <t>※ [공통] 담당 컴포넌트는 Interface 기준 표기이다. 선언부는 Interface 에, 실제 로직은 구현체 클래스에 작성한다. 현행 구현체 : RequestContextResolver→HttpHeaderRequestContextResolver, ClientAuthenticationService→DummyClientAuthenticationService, ServiceMetadataRepository→InMemoryServiceMetadataRepository, AuthorizationService→DummyAuthorizationService. Dummy·InMemory 구현체는 DB 연동 시 교체 대상이다.</t>
         </is>
       </c>
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] role_code 의 액션은 inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력) 5종이나, Phase 1 의 REST API 는 조회만 수행하므로 inqy 로 고정된다. 따라서 사용자 권한과 서비스 권한의 다대다 대조는 발생하지 않는다.</t>
+          <t>※ [2단계] 설계서 5.2 의 "미입력 시 서버 생성" 에서 서버는 별도의 채번 서버가 아니라 요청을 수신한 BSL WAS 인스턴스 자신을 뜻한다. 호출자가 X-Request-ID 를 보내지 않아도 요청 단위 추적 키는 반드시 있어야 하므로, BSL 이 직접 REQ-yyyyMMdd-0000 형식으로 채번한다.</t>
         </is>
       </c>
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 사용자 화면권한은 기존 IFRS17 권한 테이블을 Join 하여 취득하는 값이므로 Request 입력 항목이 아니다.</t>
+          <t>※ [2단계] request_id 가 반드시 필요한 이유는 BS_CALL_LOG 의 PK 이자 설계서 12.3 장애 대응의 추적 기준 키이기 때문이다. 8단계 감사 시작 로그는 PK 없이 INSERT 할 수 없으므로 2단계에서 값을 확정한다.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>※ [6단계] 담당 컴포넌트 AuthorizationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 authorizeService 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+          <t>※ [2단계] request_id 는 호출자 입력 여부와 무관하게 항상 서버가 채번한다. 호출자가 보낸 X-Request-ID 는 PK 로 사용하지 않고 client_request_id 에 원본 그대로 보관하여, 외부 값의 형식 불일치와 중복 전송으로 인한 PK 충돌을 구조적으로 차단한다.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 파라미터의 데이터 타입·형식 검증은 별도 세부 단계로 두지 않는다. BS_SERVICE_PARAM 에 param_type (STRING/NUMBER/BOOLEAN/DATE 등) 이 정의되어 있으나, 타입 불일치는 (2) DTO 바인딩 시 변환 실패로 걸러지므로 추가 코드가 필요하지 않다.</t>
+          <t>※ [2단계] 위 정책은 설계서 5.2 및 BSL-F-07 판정 기준(TC-07-2 — X-Request-ID 전송 시 응답 requestId 가 동일 값)과 다르다. 응답 Envelope 의 requestId 를 서버 채번값으로 반환할지, 호출자 원본을 clientRequestId 로 함께 반환할지는 11단계 표준 JSON 변환 상세화 시 확정한다.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 허용값·허용범위 검증은 이번 구현 범위에서 제외한다. 서비스별 업무 규칙 성격이 강해 공통 단계에서 테이블 기반으로 일반화하면 코드량이 커지며, 설계서 10.2 예시와 같이 BusinessServiceHandler.validate() 에서 서비스별로 처리한다. 이에 따라 부록 A 의 BS-VAL-002(허용범위 초과)는 이번 구현 범위에서 발생 지점이 없다.</t>
+          <t>※ [2단계] 2단계는 request_id 와 client_request_id 값을 확정하여 ServiceContext 에 보관하는 단계이며, BS_CALL_LOG 실제 INSERT 는 8단계 감사 시작 로그 기록에서 수행한다.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 검증 기준 데이터는 BS_SERVICE_PARAM 을 사용한다. BS_SERVICE_VERSION.request_schema 는 5단계 Service Catalog 활성 버전 조회의 대상 테이블 컬럼이므로 7단계 판정에는 사용하지 않는다.</t>
+          <t>※ [2단계] X-Trace-ID 도 미입력 시 서버가 TRACE-yyyyMMdd-0000 으로 채번한다. 다만 Trace ID 는 BS_CALL_LOG 의 PK 가 아니므로 재채번 대상이 아니며, 호출자 입력값이 있으면 그대로 사용한다.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 업무 파라미터 기반 추가 권한 확인(6.1 인증과 권한 흐름 5항)은 이번 구현 범위에서 제외한다. 사용자 권한 판정은 4단계 사용자 Context 와 6단계 서비스/역할 권한 확인에서 종결되며, Phase 1 조회 서비스의 파라미터(기준년월·회계기준·보고서유형 등)에는 사용자별 접근 범위를 가르는 식별자가 없다. 설계서 10.2 예시도 해당 확인을 "필요 시" 조건부로 기술한다.</t>
+          <t>※ [2단계] IdGenerator 는 WAS 단일 인스턴스 기준 In-Memory AtomicInteger 채번이므로 다중 WAS 환경에서 동일 request_id 가 채번될 수 있다. 설계서 5.2 · BSL-F-07 실구현 시 조치에 따라 server_instance 를 포함한 채번 정책으로 교체해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="34" t="inlineStr">
         <is>
-          <t>※ [7단계] 필수 파라미터 판정 컬럼은 BS_SERVICE_PARAM.required_yn (char(1), DEFAULT 'Y', Y(필수)/N(선택)) 이며, 테이블 설계서 확인으로 확정하였다. param_description 은 설명 항목, display_order 는 화면 표시 순서 항목이므로 7단계 판정에는 사용하지 않는다.</t>
+          <t>※ [2단계] BS_CALL_LOG.client_request_id 는 테이블 설계서 시트를 확인하지 못했다. 컬럼 존재 여부·타입·길이는 시트 확인 후 확정하며, 확정 시 ServiceContext 와 BsCallLog 에 clientRequestId 필드를 신설한다.</t>
         </is>
       </c>
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="34" t="inlineStr">
         <is>
-          <t>※ 각 단계의 DB 접속 실패 등 인프라 오류는 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
+          <t>※ [3단계] 호출 Client 검증 단계에서는 BS_CLIENT 테이블만 조회하며, BS_CLIENT_SERVICE 테이블에는 접근하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="34" t="inlineStr">
         <is>
-          <t>※ 예외 처리 절차(예외 클래스·실패 감사 로그·표준 Error Response 조립)는 기능 관점의 본 표와 성격이 달라 제외하였으며, 구현 착수 시점에 별도 표로 작성한다.</t>
+          <t>※ [3단계] 세부 단계 (2) 는 BS_CLIENT 등록 여부와 active_yn = 'Y' 를 하나의 단계에서 판정하며, 두 경우 모두 부록 A 의 BS-AUTH-001(401) 로 처리한다. 미등록과 비활성은 응답 오류코드로 구분되지 않으며, 오류코드명과 감사 로그로 식별한다.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="34" t="inlineStr">
         <is>
-          <t>※ [12단계 상세화 시 반영] 최종 허용/거부 결과의 감사 기록(authorization_result) 을 포함한다. 근거 : 6.1 인증과 권한 흐름 6항 / 6.3 감사로그 필수항목 — 보안 | remote_ip, auth_type, authorization_result.</t>
+          <t>※ [3단계] 담당 컴포넌트 ClientAuthenticationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 validateClient 단계를 담당할 컴포넌트로 명명한 것이다.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="34" t="inlineStr">
         <is>
-          <t>※ 1~2 · 8~13 단계의 세부 단계·현황·담당 컴포넌트·수정 대상·오류코드·오류코드명은 후속 상세화 시 기입한다. 4단계는 이번 구현 미대상이다.</t>
+          <t>※ [5단계] 세부 단계 (2) 는 BS_SERVICE.active_yn = 'Y', (4) 는 BS_SERVICE_VERSION.status_code = 'ACTIVE' 를 판정한다. 두 테이블의 상태 컬럼명이 서로 다른 점에 유의한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="34" t="inlineStr">
+        <is>
+          <t>※ [6단계] 세부 단계 (2) 는 BS_SERVICE_ROLE 에 active_yn 컬럼이 없으므로 상태값을 판정하지 않는다. 테이블 설계서의 BS_SERVICE_ROLE 정의에 따라 필요 권한 코드(화면ID:액션) 존재 여부와 외부 권한 API 의 사용자 화면권한(Y/N) 을 AND 비교하여 판정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t>※ [6단계] role_code 의 액션은 inqy(조회)/sv(저장)/cnfr(확정)/aprl(승인)/prt(출력) 5종이나, Phase 1 의 REST API 는 조회만 수행하므로 inqy 로 고정된다. 따라서 사용자 권한과 서비스 권한의 다대다 대조는 발생하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>※ [6단계] 사용자 화면권한은 기존 IFRS17 권한 테이블을 Join 하여 취득하는 값이므로 Request 입력 항목이 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="34" t="inlineStr">
+        <is>
+          <t>※ [6단계] 담당 컴포넌트 AuthorizationService 는 설계서 4.2 에 명시된 컴포넌트가 아니며, 10.4 의사코드의 authorizeService 단계를 담당할 컴포넌트로 명명한 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 파라미터의 데이터 타입·형식 검증은 별도 세부 단계로 두지 않는다. BS_SERVICE_PARAM 에 param_type (STRING/NUMBER/BOOLEAN/DATE 등) 이 정의되어 있으나, 타입 불일치는 (2) DTO 바인딩 시 변환 실패로 걸러지므로 추가 코드가 필요하지 않다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 허용값·허용범위 검증은 이번 구현 범위에서 제외한다. 서비스별 업무 규칙 성격이 강해 공통 단계에서 테이블 기반으로 일반화하면 코드량이 커지며, 설계서 10.2 예시와 같이 BusinessServiceHandler.validate() 에서 서비스별로 처리한다. 이에 따라 부록 A 의 BS-VAL-002(허용범위 초과)는 이번 구현 범위에서 발생 지점이 없다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 검증 기준 데이터는 BS_SERVICE_PARAM 을 사용한다. BS_SERVICE_VERSION.request_schema 는 5단계 Service Catalog 활성 버전 조회의 대상 테이블 컬럼이므로 7단계 판정에는 사용하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 업무 파라미터 기반 추가 권한 확인(6.1 인증과 권한 흐름 5항)은 이번 구현 범위에서 제외한다. 사용자 권한 판정은 4단계 사용자 Context 와 6단계 서비스/역할 권한 확인에서 종결되며, Phase 1 조회 서비스의 파라미터(기준년월·회계기준·보고서유형 등)에는 사용자별 접근 범위를 가르는 식별자가 없다. 설계서 10.2 예시도 해당 확인을 "필요 시" 조건부로 기술한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="34" t="inlineStr">
+        <is>
+          <t>※ [7단계] 필수 파라미터 판정 컬럼은 BS_SERVICE_PARAM.required_yn (char(1), DEFAULT 'Y', Y(필수)/N(선택)) 이며, 테이블 설계서 확인으로 확정하였다. param_description 은 설명 항목, display_order 는 화면 표시 순서 항목이므로 7단계 판정에는 사용하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="34" t="inlineStr">
+        <is>
+          <t>※ 각 단계의 DB 접속 실패 등 인프라 오류는 판정 실패와 성격이 달라 BS-SYS-500(내부 시스템 오류) 대상이며, 본 표에는 포함하지 않았다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="34" t="inlineStr">
+        <is>
+          <t>※ 예외 처리 절차(예외 클래스·실패 감사 로그·표준 Error Response 조립)는 기능 관점의 본 표와 성격이 달라 제외하였으며, 구현 착수 시점에 별도 표로 작성한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="34" t="inlineStr">
+        <is>
+          <t>※ [12단계 상세화 시 반영] 최종 허용/거부 결과의 감사 기록(authorization_result) 을 포함한다. 근거 : 6.1 인증과 권한 흐름 6항 / 6.3 감사로그 필수항목 — 보안 | remote_ip, auth_type, authorization_result.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="34" t="inlineStr">
+        <is>
+          <t>※ 1 · 8~13 단계의 세부 단계·현황·담당 컴포넌트·수정 대상·오류코드·오류코드명은 후속 상세화 시 기입한다. 4단계는 이번 구현 미대상이다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="63">
     <mergeCell ref="A65:I65"/>
-    <mergeCell ref="A46:I46"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="A75:I75"/>
+    <mergeCell ref="A66:I66"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="A7:A8"/>
     <mergeCell ref="A56:I56"/>
-    <mergeCell ref="A11:A14"/>
+    <mergeCell ref="A78:I78"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="B46:I46"/>
+    <mergeCell ref="A50:I50"/>
     <mergeCell ref="B31:I31"/>
-    <mergeCell ref="B11:B14"/>
-    <mergeCell ref="B27:I27"/>
     <mergeCell ref="A55:I55"/>
-    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="B43:I43"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A71:I71"/>
     <mergeCell ref="B39:I39"/>
-    <mergeCell ref="A47:I47"/>
+    <mergeCell ref="A76:I76"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B42:I42"/>
     <mergeCell ref="A53:I53"/>
+    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="A18:A19"/>
     <mergeCell ref="A62:I62"/>
-    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="A72:I72"/>
     <mergeCell ref="A52:I52"/>
-    <mergeCell ref="A43:I43"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B44:I44"/>
+    <mergeCell ref="A68:I68"/>
     <mergeCell ref="A63:I63"/>
     <mergeCell ref="B29:I29"/>
-    <mergeCell ref="A17:A18"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="B34:I34"/>
-    <mergeCell ref="A44:I44"/>
     <mergeCell ref="B28:I28"/>
+    <mergeCell ref="A67:I67"/>
     <mergeCell ref="B37:I37"/>
     <mergeCell ref="A58:I58"/>
+    <mergeCell ref="A77:I77"/>
     <mergeCell ref="A48:I48"/>
     <mergeCell ref="B40:I40"/>
     <mergeCell ref="A64:I64"/>
     <mergeCell ref="A59:I59"/>
+    <mergeCell ref="A73:I73"/>
     <mergeCell ref="B30:I30"/>
+    <mergeCell ref="A51:I51"/>
     <mergeCell ref="A49:I49"/>
-    <mergeCell ref="A51:I51"/>
     <mergeCell ref="B33:I33"/>
+    <mergeCell ref="A9:A10"/>
     <mergeCell ref="A60:I60"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="A70:I70"/>
     <mergeCell ref="B36:I36"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="A61:I61"/>
+    <mergeCell ref="B45:I45"/>
+    <mergeCell ref="A69:I69"/>
     <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B32:I32"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -847,7 +847,7 @@
       <c r="C7" s="14" t="inlineStr">
         <is>
           <t>(1) 필수 Header 의 X-Request-ID 가 입력되었는지 체크한다.
-→ 미입력이면 서버(BSL WAS)가 BS_CALL_LOG 의 PK 양식(REQ-yyyyMMdd-0000)으로 채번하여 request_id 를 확정하고 다음 프로세스 진행
+→ 미입력이면 client_request_id 를 적재하지 않고(NULL), 서버가 request_id 를 채번하여 다음 프로세스 진행
 → 입력되어 있으면 (2) 단계 진행</t>
         </is>
       </c>
@@ -891,8 +891,8 @@
       <c r="B8" s="26" t="n"/>
       <c r="C8" s="21" t="inlineStr">
         <is>
-          <t>(2) 입력된 X-Request-ID 원본을 BS_CALL_LOG 의 client_request_id 컬럼 적재값으로 확정하고,
-PK 인 request_id 는 서버가 PK 양식(REQ-yyyyMMdd-0000)으로 재채번한다.
+          <t>(2) 입력된 X-Request-ID 를 BS_CALL_LOG 의 client_request_id 적재값으로 원본 그대로 확정하고,
+PK 인 request_id 는 호출자 헤더를 사용하지 않고 서버가 PK 양식(REQ-yyyyMMddHHmmssSSS-n)으로 별도 채번한다.
 → request_id 와 client_request_id 가 모두 확정되면 다음 프로세스 진행</t>
         </is>
       </c>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>테이블 설계서 BS_CALL_LOG (business_service.bs_call_log, PK request_id) — 6.3 감사로그 필수항목 · 7.3 핵심 DDL 의 호출 이력 저장 테이블   /   client_request_id 컬럼은 테이블 설계서 시트로 확인하지 못했다 (현행 스켈레톤 BsCallLog.java 에 미정의)</t>
+          <t>테이블 설계서 BS_CALL_LOG (business_service.bs_call_log, 논리명 호출 감사로그, PK request_id) — request_id varchar(80) NOT NULL, "호출 요청 고유 ID — 서버 생성 유일값(호출자 헤더 미사용). 코드 반영 예정" [핵심 로직], 예) REQ-20260714093012345-1   ·   client_request_id varchar(80) NULL, "[신규] 호출자 X-Request-ID 원본(추적·상관용, 유일성 미보장·중복 가능)", 예) REQ-20260714-0001   ·   trace_id varchar(80) NULL, "분산추적/장애분석용 선택 pass-through(§5.2 X-Trace-ID, 응답 에코). 운영 주 추적키는 request_id", 예) TRACE-abc123   /   출처 : 상세설계서 v1.3 §7.3 (원본) + 감사 무결성 보강</t>
         </is>
       </c>
       <c r="C32" s="31" t="n"/>
@@ -1886,7 +1886,7 @@
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="34" t="inlineStr">
         <is>
-          <t>※ [2단계] 설계서 5.2 의 "미입력 시 서버 생성" 에서 서버는 별도의 채번 서버가 아니라 요청을 수신한 BSL WAS 인스턴스 자신을 뜻한다. 호출자가 X-Request-ID 를 보내지 않아도 요청 단위 추적 키는 반드시 있어야 하므로, BSL 이 직접 REQ-yyyyMMdd-0000 형식으로 채번한다.</t>
+          <t>※ [2단계] 설계서 5.2 의 "미입력 시 서버 생성" 에서 서버는 별도의 채번 서버가 아니라 요청을 수신한 BSL WAS 인스턴스 자신을 뜻한다. 호출자가 X-Request-ID 를 보내지 않아도 요청 단위 추적 키는 반드시 있어야 하므로, BSL 이 직접 request_id 를 채번한다. 따라서 X-Request-ID 에는 필수 입력 조건을 두지 않는다.</t>
         </is>
       </c>
     </row>
@@ -1900,14 +1900,14 @@
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="34" t="inlineStr">
         <is>
-          <t>※ [2단계] request_id 는 호출자 입력 여부와 무관하게 항상 서버가 채번한다. 호출자가 보낸 X-Request-ID 는 PK 로 사용하지 않고 client_request_id 에 원본 그대로 보관하여, 외부 값의 형식 불일치와 중복 전송으로 인한 PK 충돌을 구조적으로 차단한다.</t>
+          <t>※ [2단계] request_id 는 호출자 입력 여부와 무관하게 항상 서버가 독립 채번한다. 테이블 설계서 BS_CALL_LOG 의 request_id 용도에 "서버 생성 유일값(호출자 헤더 미사용)" 이 명시되어 있으므로, 호출자가 보낸 X-Request-ID 값은 request_id 산출의 입력으로 사용하지 않는다. 세부 단계 (1)·(2) 의 채번 로직은 동일하며, 두 단계의 차이는 client_request_id 적재 여부뿐이다.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>※ [2단계] 위 정책은 설계서 5.2 및 BSL-F-07 판정 기준(TC-07-2 — X-Request-ID 전송 시 응답 requestId 가 동일 값)과 다르다. 응답 Envelope 의 requestId 를 서버 채번값으로 반환할지, 호출자 원본을 clientRequestId 로 함께 반환할지는 11단계 표준 JSON 변환 상세화 시 확정한다.</t>
+          <t>※ [2단계] 호출자 X-Request-ID 를 PK 로 쓰지 않는 이유는 테이블 설계서가 client_request_id 를 "유일성 미보장·중복 가능" 으로 정의하기 때문이다. 외부 입력값을 PK 로 사용하면 호출자가 같은 값을 재전송할 때 감사 로그 INSERT 가 실패하므로, 유일성은 서버 채번값으로 보장하고 호출자 값은 추적·상관용으로만 원본 보관한다(감사 무결성).</t>
         </is>
       </c>
     </row>
@@ -1921,21 +1921,21 @@
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="34" t="inlineStr">
         <is>
-          <t>※ [2단계] X-Trace-ID 도 미입력 시 서버가 TRACE-yyyyMMdd-0000 으로 채번한다. 다만 Trace ID 는 BS_CALL_LOG 의 PK 가 아니므로 재채번 대상이 아니며, 호출자 입력값이 있으면 그대로 사용한다.</t>
+          <t>※ [2단계] request_id 의 PK 양식은 테이블 설계서 예시 REQ-20260714093012345-1 기준으로 REQ-yyyyMMddHHmmssSSS-n 이다. 현행 IdGenerator.newRequestId() 는 REQ-yyyyMMdd-0000 (일자 + In-Memory AtomicInteger) 이므로 교체 대상이며, 테이블 설계서에도 "코드 반영 예정" 으로 표기되어 있다. 다중 WAS 환경의 유일성은 server_instance 를 포함한 채번 정책으로 보장한다.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="34" t="inlineStr">
         <is>
-          <t>※ [2단계] IdGenerator 는 WAS 단일 인스턴스 기준 In-Memory AtomicInteger 채번이므로 다중 WAS 환경에서 동일 request_id 가 채번될 수 있다. 설계서 5.2 · BSL-F-07 실구현 시 조치에 따라 server_instance 를 포함한 채번 정책으로 교체해야 한다.</t>
+          <t>※ [2단계] trace_id 는 테이블 설계서상 NULL 허용의 선택 pass-through 컬럼이며(§5.2 X-Trace-ID 를 응답에 에코), 운영 주 추적키는 request_id 이다. 따라서 X-Trace-ID 는 호출자 입력값이 있으면 그대로 사용하고 재채번하지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="34" t="inlineStr">
         <is>
-          <t>※ [2단계] BS_CALL_LOG.client_request_id 는 테이블 설계서 시트를 확인하지 못했다. 컬럼 존재 여부·타입·길이는 시트 확인 후 확정하며, 확정 시 ServiceContext 와 BsCallLog 에 clientRequestId 필드를 신설한다.</t>
+          <t>※ [2단계] 응답 Envelope 의 requestId 는 서버 채번값을 반환한다. 설계서 BSL-F-07 판정 기준(TC-07-2 — 전송한 X-Request-ID 와 응답 requestId 가 동일)은 감사 무결성 보강으로 대체되며, 호출자 값의 상관 추적은 client_request_id 와 trace_id 응답 에코가 담당한다. 응답 필드 노출 여부는 11단계 표준 JSON 변환 상세화 시 확정한다.</t>
         </is>
       </c>
     </row>
@@ -2070,11 +2070,11 @@
     <mergeCell ref="A78:I78"/>
     <mergeCell ref="A3:I3"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A74:I74"/>
+    <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="B31:I31"/>
     <mergeCell ref="A55:I55"/>
+    <mergeCell ref="A74:I74"/>
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="A57:I57"/>
     <mergeCell ref="A2:I2"/>
@@ -2084,7 +2084,6 @@
     <mergeCell ref="A12:A15"/>
     <mergeCell ref="B42:I42"/>
     <mergeCell ref="A53:I53"/>
-    <mergeCell ref="B32:I32"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="A62:I62"/>
     <mergeCell ref="A72:I72"/>
@@ -2094,6 +2093,7 @@
     <mergeCell ref="A68:I68"/>
     <mergeCell ref="A63:I63"/>
     <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B35:I35"/>
     <mergeCell ref="B38:I38"/>
     <mergeCell ref="B34:I34"/>
     <mergeCell ref="B28:I28"/>
@@ -2121,7 +2121,7 @@
     <mergeCell ref="B45:I45"/>
     <mergeCell ref="A69:I69"/>
     <mergeCell ref="B41:I41"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="B32:I32"/>
     <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -1907,7 +1907,7 @@
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="34" t="inlineStr">
         <is>
-          <t>※ [2단계] 호출자 X-Request-ID 를 PK 로 쓰지 않는 이유는 테이블 설계서가 client_request_id 를 "유일성 미보장·중복 가능" 으로 정의하기 때문이다. 외부 입력값을 PK 로 사용하면 호출자가 같은 값을 재전송할 때 감사 로그 INSERT 가 실패하므로, 유일성은 서버 채번값으로 보장하고 호출자 값은 추적·상관용으로만 원본 보관한다(감사 무결성).</t>
+          <t>※ [2단계] client_request_id 는 판정에 관여하지 않는 정보성 컬럼이다(추적·상관용). 테이블 설계서가 이 컬럼을 "유일성 미보장·중복 가능" 으로 정의하므로, 이 값을 기반으로 request_id 를 생성하면 호출자가 같은 X-Request-ID 를 재전송할 때 채번·INSERT 가 실패한다. 따라서 유일성은 서버 채번값으로 보장하고, 호출자 값은 원본 그대로 보관만 한다(감사 무결성).</t>
         </is>
       </c>
     </row>
@@ -2072,8 +2072,8 @@
     <mergeCell ref="A16:A17"/>
     <mergeCell ref="B31:I31"/>
     <mergeCell ref="B46:I46"/>
+    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A50:I50"/>
-    <mergeCell ref="A55:I55"/>
     <mergeCell ref="A74:I74"/>
     <mergeCell ref="B43:I43"/>
     <mergeCell ref="A57:I57"/>

--- a/docs/IFRS17BSL기능정의서_v2.4.xlsx
+++ b/docs/IFRS17BSL기능정의서_v2.4.xlsx
@@ -935,8 +935,14 @@
       </c>
     </row>
     <row r="9" ht="50" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="35" t="n"/>
+      <c r="A9" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>호출 Client 검증</t>
+        </is>
+      </c>
       <c r="C9" s="21" t="inlineStr">
         <is>
           <t>(1) 필수 Header 의 X-Client-ID 가 아예 입력되지 않았는지 필수입력값 유효성을 체크한다.
@@ -1047,8 +1053,14 @@
       <c r="I11" s="18" t="inlineStr"/>
     </row>
     <row r="12" ht="50" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="35" t="n"/>
+      <c r="A12" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="35" t="inlineStr">
+        <is>
+          <t>Service Catalog에서 활성 버전 조회</t>
+        </is>
+      </c>
       <c r="C12" s="21" t="inlineStr">
         <is>
           <t>(1) service ID 가 존재하는지
@@ -1215,8 +1227,14 @@
       </c>
     </row>
     <row r="16" ht="50" customHeight="1">
-      <c r="A16" s="35" t="n"/>
-      <c r="B16" s="35" t="n"/>
+      <c r="A16" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B16" s="35" t="inlineStr">
+        <is>
+          <t>서비스/역할 권한 확인</t>
+        </is>
+      </c>
       <c r="C16" s="21" t="inlineStr">
         <is>
           <t>(1) 테이블 BS_CLIENT_SERVICE 의 PK 인 (client_id, service_id) 가 (X-Client-ID Header 값, 요청 serviceId) 와
@@ -1309,8 +1327,14 @@
       </c>
     </row>
     <row r="18" ht="50" customHeight="1">
-      <c r="A18" s="35" t="n"/>
-      <c r="B18" s="35" t="n"/>
+      <c r="A18" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" s="35" t="inlineStr">
+        <is>
+          <t>입력 Schema 및 업무 파라미터 검증</t>
+        </is>
+      </c>
       <c r="C18" s="21" t="inlineStr">
         <is>
           <t>(1) 테이블 BS_SERVICE_PARAM 의 PK 인 (service_id, version, param_name) 로 요청 serviceId 와 확정 version 의
@@ -1818,6 +1842,11 @@
           <t>7단계 · 담당 컴포넌트</t>
         </is>
       </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>4.3-12 입력 Schema 및 업무 파라미터 검증   /   10.4 공통 Executor 의사코드 — authorizeService 이후 invokeHandler 이전   /   현행 코드 StandardRequestValidator.validate(StandardRequest, ServiceMetadata) · ParameterBinder.bind(Map, Class)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="33" t="inlineStr">
@@ -1825,6 +1854,11 @@
           <t>7단계 · 오류코드</t>
         </is>
       </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>부록 A 표준 오류코드 — BS-VAL-001 | 400 | 필수값 누락 또는 형식 오류   /   4.5 예외 처리 기준 — 입력 오류 | 400 | BS-VAL-001 | 필드별 오류 반환, Stack Trace 금지   /   11.2 필수 인수 시나리오 — 입력 오류 | 잘못된 YYYY-MM | 400/BS-VAL-001</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="33" t="inlineStr">
@@ -1832,11 +1866,21 @@
           <t>7단계 · 참조 데이터</t>
         </is>
       </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>테이블 설계서 BS_SERVICE_PARAM (business_service.bs_service_param, 논리명 입력 파라미터 정의, PK service_id + version + param_name) — required_yn char(1) NOT NULL DEFAULT 'Y', Y(필수)/N(선택), "필수 여부"   ·   param_type varchar(30) NOT NULL, STRING/NUMBER/BOOLEAN/DATE 등, "파라미터 데이터 타입"   ·   param_description varchar(300), "파라미터 설명"   ·   display_order integer NOT NULL DEFAULT 1, "화면 표시 순서"   /   service_id 는 FK→BS_SERVICE_VERSION, version 은 FK   /   출처 : 상세설계서 v1.3 §7.2 (신규)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="33" t="inlineStr">
         <is>
           <t>6단계 · 권한 원칙</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>6.2 권한 원칙 — 서비스 권한은 BS_SERVICE_ROLE 과 기존 IFRS17 권한정보를 함께 사용한다   /   테이블 설계서 BS_SERVICE_ROLE 설명 — "외부 권한API의 사용자 화면권한(Y/N)과 AND 비교(§6.2 권한 원칙)"</t>
         </is>
       </c>
     </row>
